--- a/projects/P_010_Current_Market_Posture/data/excel_exports/History Grid (SPY)_v3.xlsx
+++ b/projects/P_010_Current_Market_Posture/data/excel_exports/History Grid (SPY)_v3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="27">
   <si>
     <t>High
 Price</t>
@@ -150,10 +150,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" readingOrder="0"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V44"/>
+  <dimension ref="A1:V45"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
@@ -462,8 +462,8 @@
     <col min="8" max="10" width="14.5703125" customWidth="1"/>
     <col min="11" max="11" width="12.42578125" customWidth="1"/>
     <col min="12" max="12" width="13.42578125" customWidth="1"/>
-    <col min="13" max="13" width="8.28515625" customWidth="1"/>
-    <col min="14" max="14" width="17.28515625" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" customWidth="1"/>
+    <col min="14" max="14" width="15.85546875" customWidth="1"/>
     <col min="15" max="15" width="12.85546875" customWidth="1"/>
     <col min="16" max="16" width="17.7109375" customWidth="1"/>
     <col min="17" max="17" width="10" customWidth="1"/>
@@ -477,37 +477,37 @@
       <c r="A1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K1" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="M1" t="s">
@@ -519,27 +519,27 @@
       <c r="Q1" t="s">
         <v>3</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="L2" s="2"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="L2" s="1"/>
       <c r="M2" t="s">
         <v>4</v>
       </c>
@@ -561,2864 +561,2932 @@
       <c r="S2" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="1">
-        <v>46247</v>
+      <c r="A3" s="2">
+        <v>46261</v>
       </c>
       <c r="B3">
-        <v>2.138427734375</v>
+        <v>2.62762451171875</v>
       </c>
       <c r="C3">
-        <v>5.8125</v>
+        <v>-0.08984375</v>
       </c>
       <c r="D3">
-        <v>13.65576171875</v>
+        <v>-1.89813232421875</v>
       </c>
       <c r="E3">
-        <v>774.869995117188</v>
+        <v>768.5</v>
       </c>
       <c r="F3">
-        <v>779.369995117188</v>
+        <v>772.35498046875</v>
       </c>
       <c r="G3">
-        <v>774.111022949219</v>
+        <v>767.159973144531</v>
       </c>
       <c r="H3">
-        <v>777.880004882813</v>
+        <v>771.099975585938</v>
       </c>
       <c r="I3">
-        <v>779.426086425781</v>
+        <v>772.763793945313</v>
       </c>
       <c r="J3">
-        <v>774.595520019531</v>
+        <v>768.268737792969</v>
       </c>
       <c r="K3">
-        <v>35634400</v>
+        <v>34557000</v>
       </c>
       <c r="L3">
-        <v>0.0119076687842607</v>
+        <v>0.435235887765884</v>
       </c>
       <c r="M3">
-        <v>41.8410453796387</v>
+        <v>81.5614852905273</v>
       </c>
       <c r="N3">
-        <v>-30.5117282867432</v>
+        <v>-9.15767955780029</v>
       </c>
       <c r="O3" t="s">
         <v>1</v>
       </c>
       <c r="P3">
-        <v>25.7974395751953</v>
+        <v>27.7463893890381</v>
       </c>
       <c r="Q3">
-        <v>774.528503417969</v>
+        <v>768.216796875</v>
       </c>
       <c r="R3">
-        <v>769.578063964844</v>
+        <v>767.635192871094</v>
       </c>
       <c r="S3">
-        <v>761.106079101563</v>
+        <v>765.716247558594</v>
       </c>
       <c r="T3">
-        <v>0.05609130859375</v>
+        <v>0.4088134765625</v>
       </c>
       <c r="U3">
-        <v>0.4844970703125</v>
+        <v>1.1087646484375</v>
       </c>
       <c r="V3">
-        <v>4.83056640625</v>
+        <v>4.49505615234375</v>
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="1">
-        <v>46246</v>
+      <c r="A4" s="2">
+        <v>46260</v>
       </c>
       <c r="B4">
-        <v>0.5604248046875</v>
+        <v>1.0751953125</v>
       </c>
       <c r="C4">
-        <v>6.97613525390625</v>
+        <v>-2.80926513671875</v>
       </c>
       <c r="D4">
-        <v>14.05029296875</v>
+        <v>-2.94293212890625</v>
       </c>
       <c r="E4">
-        <v>774.710021972656</v>
+        <v>764.72998046875</v>
       </c>
       <c r="F4">
-        <v>774.900024414063</v>
+        <v>767.349975585938</v>
       </c>
       <c r="G4">
-        <v>771.280029296875</v>
+        <v>763.929992675781</v>
       </c>
       <c r="H4">
-        <v>772.489990234375</v>
+        <v>766.080017089844</v>
       </c>
       <c r="I4">
-        <v>774.973022460938</v>
+        <v>768.207458496094</v>
       </c>
       <c r="J4">
-        <v>770.355773925781</v>
+        <v>764.246948242188</v>
       </c>
       <c r="K4">
-        <v>33179100</v>
+        <v>28751500</v>
       </c>
       <c r="L4">
-        <v>-0.104282923042774</v>
+        <v>-0.18904621899128</v>
       </c>
       <c r="M4">
-        <v>60.2131042480469</v>
+        <v>89.783576965332</v>
       </c>
       <c r="N4">
-        <v>1.56267952919006</v>
+        <v>4.61834716796875</v>
       </c>
       <c r="O4" t="s">
         <v>1</v>
       </c>
       <c r="P4">
-        <v>3.13029456138611</v>
+        <v>13.1619310379028</v>
       </c>
       <c r="Q4">
-        <v>771.74609375</v>
+        <v>765.718139648438</v>
       </c>
       <c r="R4">
-        <v>767.270751953125</v>
+        <v>766.658386230469</v>
       </c>
       <c r="S4">
-        <v>759.28759765625</v>
+        <v>765.115905761719</v>
       </c>
       <c r="T4">
-        <v>0.072998046875</v>
+        <v>0.85748291015625</v>
       </c>
       <c r="U4">
-        <v>-0.92425537109375</v>
+        <v>0.31695556640625</v>
       </c>
       <c r="V4">
-        <v>4.61724853515625</v>
+        <v>3.96051025390625</v>
       </c>
     </row>
     <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="1">
-        <v>46245</v>
+      <c r="A5" s="2">
+        <v>46259</v>
       </c>
       <c r="B5">
-        <v>0.1639404296875</v>
+        <v>-0.21295166015625</v>
       </c>
       <c r="C5">
-        <v>10.3299560546875</v>
+        <v>-3.71630859375</v>
       </c>
       <c r="D5">
-        <v>14.33642578125</v>
+        <v>-3.156005859375</v>
       </c>
       <c r="E5">
-        <v>774.530029296875</v>
+        <v>766.159973144531</v>
       </c>
       <c r="F5">
-        <v>774.609985351563</v>
+        <v>766.780029296875</v>
       </c>
       <c r="G5">
-        <v>769.200012207031</v>
+        <v>763.050109863281</v>
       </c>
       <c r="H5">
-        <v>770.559997558594</v>
+        <v>765.909973144531</v>
       </c>
       <c r="I5">
-        <v>772.776306152344</v>
+        <v>767.72802734375</v>
       </c>
       <c r="J5">
-        <v>768.681701660156</v>
+        <v>762.958129882813</v>
       </c>
       <c r="K5">
-        <v>36740500</v>
+        <v>27422200</v>
       </c>
       <c r="L5">
-        <v>0.0452444888651371</v>
+        <v>-0.173810690641403</v>
       </c>
       <c r="M5">
-        <v>59.2866439819336</v>
+        <v>85.8201065063477</v>
       </c>
       <c r="N5">
-        <v>5.286705493927</v>
+        <v>-4.07025098800659</v>
       </c>
       <c r="O5" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P5">
-        <v>-12.588695526123</v>
+        <v>17.5014266967773</v>
       </c>
       <c r="Q5">
-        <v>770.895874023438</v>
+        <v>765.25634765625</v>
       </c>
       <c r="R5">
-        <v>765.665771484375</v>
+        <v>766.761657714844</v>
       </c>
       <c r="S5">
-        <v>757.667053222656</v>
+        <v>764.921325683594</v>
       </c>
       <c r="T5">
-        <v>-1.83367919921875</v>
+        <v>0.947998046875</v>
       </c>
       <c r="U5">
-        <v>-0.518310546875</v>
+        <v>-0.09197998046875</v>
       </c>
       <c r="V5">
-        <v>4.0946044921875</v>
+        <v>4.7698974609375</v>
       </c>
     </row>
     <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="1">
-        <v>46244</v>
+      <c r="A6" s="2">
+        <v>46258</v>
       </c>
       <c r="B6">
-        <v>1.07012939453125</v>
+        <v>-1.30682373046875</v>
       </c>
       <c r="C6">
-        <v>12.7230834960938</v>
+        <v>-4.25238037109375</v>
       </c>
       <c r="D6">
-        <v>14.5609741210938</v>
+        <v>-3.29644775390625</v>
       </c>
       <c r="E6">
-        <v>772.599975585938</v>
+        <v>764.780029296875</v>
       </c>
       <c r="F6">
-        <v>775.049987792969</v>
+        <v>765.219970703125</v>
       </c>
       <c r="G6">
-        <v>771.619995117188</v>
+        <v>762.080017089844</v>
       </c>
       <c r="H6">
-        <v>773.030029296875</v>
+        <v>763.469970703125</v>
       </c>
       <c r="I6">
-        <v>774.887023925781</v>
+        <v>765.826171875</v>
       </c>
       <c r="J6">
-        <v>771.254333496094</v>
+        <v>761.711730957031</v>
       </c>
       <c r="K6">
-        <v>39249400</v>
+        <v>32430800</v>
       </c>
       <c r="L6">
-        <v>0.0771513432264328</v>
+        <v>-0.439046233892441</v>
       </c>
       <c r="M6">
-        <v>56.3097152709961</v>
+        <v>89.4614105224609</v>
       </c>
       <c r="N6">
-        <v>0.722540974617004</v>
+        <v>-10.5385894775391</v>
       </c>
       <c r="O6" t="s">
         <v>1</v>
       </c>
       <c r="P6">
-        <v>11.3912715911865</v>
+        <v>4.82476663589478</v>
       </c>
       <c r="Q6">
-        <v>771.117980957031</v>
+        <v>764.98291015625</v>
       </c>
       <c r="R6">
-        <v>764.006713867188</v>
+        <v>767.051391601563</v>
       </c>
       <c r="S6">
-        <v>756.085510253906</v>
+        <v>764.829284667969</v>
       </c>
       <c r="T6">
-        <v>-0.1629638671875</v>
+        <v>0.606201171875</v>
       </c>
       <c r="U6">
-        <v>-0.36566162109375</v>
+        <v>-0.3682861328125</v>
       </c>
       <c r="V6">
-        <v>3.6326904296875</v>
+        <v>4.11444091796875</v>
       </c>
     </row>
     <row r="7" ht="19.5" customHeight="1">
-      <c r="A7" s="1">
-        <v>46241</v>
+      <c r="A7" s="2">
+        <v>46255</v>
       </c>
       <c r="B7">
-        <v>2.55120849609375</v>
+        <v>-1.78106689453125</v>
       </c>
       <c r="C7">
-        <v>13.9462890625</v>
+        <v>-3.8306884765625</v>
       </c>
       <c r="D7">
-        <v>14.0487060546875</v>
+        <v>-1.76824951171875</v>
       </c>
       <c r="E7">
-        <v>771.02001953125</v>
+        <v>766.049987792969</v>
       </c>
       <c r="F7">
-        <v>773.914978027344</v>
+        <v>767.849975585938</v>
       </c>
       <c r="G7">
-        <v>769.609985351563</v>
+        <v>764.169982910156</v>
       </c>
       <c r="H7">
-        <v>773.260009765625</v>
+        <v>765.719970703125</v>
       </c>
       <c r="I7">
-        <v>774.138610839844</v>
+        <v>768.595092773438</v>
       </c>
       <c r="J7">
-        <v>768.873413085938</v>
+        <v>763.480163574219</v>
       </c>
       <c r="K7">
-        <v>43586300</v>
+        <v>39188600</v>
       </c>
       <c r="L7">
-        <v>0.194768995046616</v>
+        <v>-0.356663286685944</v>
       </c>
       <c r="M7">
-        <v>55.9057731628418</v>
+        <v>100</v>
       </c>
       <c r="N7">
-        <v>-0.691173672676086</v>
+        <v>35.2496032714844</v>
       </c>
       <c r="O7" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P7">
-        <v>3.94128084182739</v>
+        <v>-0.120509169995785</v>
       </c>
       <c r="Q7">
-        <v>769.178833007813</v>
+        <v>766.295593261719</v>
       </c>
       <c r="R7">
-        <v>761.331909179688</v>
+        <v>768.102722167969</v>
       </c>
       <c r="S7">
-        <v>754.049072265625</v>
+        <v>764.948059082031</v>
       </c>
       <c r="T7">
-        <v>0.2236328125</v>
+        <v>0.7451171875</v>
       </c>
       <c r="U7">
-        <v>-0.736572265625</v>
+        <v>-0.6898193359375</v>
       </c>
       <c r="V7">
-        <v>5.26519775390625</v>
+        <v>5.11492919921875</v>
       </c>
     </row>
     <row r="8" ht="19.5" customHeight="1">
-      <c r="A8" s="1">
-        <v>46240</v>
+      <c r="A8" s="2">
+        <v>46254</v>
       </c>
       <c r="B8">
-        <v>4.96710205078125</v>
+        <v>-4.331787109375</v>
       </c>
       <c r="C8">
-        <v>14.4755249023438</v>
+        <v>-4.02813720703125</v>
       </c>
       <c r="D8">
-        <v>12.9638061523438</v>
+        <v>0.21795654296875</v>
       </c>
       <c r="E8">
-        <v>770.210021972656</v>
+        <v>765.960021972656</v>
       </c>
       <c r="F8">
-        <v>771.820007324219</v>
+        <v>768.150024414063</v>
       </c>
       <c r="G8">
-        <v>767.460021972656</v>
+        <v>762.039978027344</v>
       </c>
       <c r="H8">
-        <v>768.559997558594</v>
+        <v>762.599975585938</v>
       </c>
       <c r="I8">
-        <v>770.416198730469</v>
+        <v>766.01708984375</v>
       </c>
       <c r="J8">
-        <v>764.270324707031</v>
+        <v>761.065002441406</v>
       </c>
       <c r="K8">
-        <v>38416800</v>
+        <v>45520300</v>
       </c>
       <c r="L8">
-        <v>0.29572406411171</v>
+        <v>-0.397614985704422</v>
       </c>
       <c r="M8">
-        <v>56.2948684692383</v>
+        <v>73.937370300293</v>
       </c>
       <c r="N8">
-        <v>-6.45771980285645</v>
+        <v>49.5063514709473</v>
       </c>
       <c r="O8" t="s">
         <v>23</v>
       </c>
       <c r="P8">
-        <v>-21.9880218505859</v>
+        <v>-31.5295848846436</v>
       </c>
       <c r="Q8">
-        <v>766.265747070313</v>
+        <v>766.6552734375</v>
       </c>
       <c r="R8">
-        <v>758.244384765625</v>
+        <v>768.666259765625</v>
       </c>
       <c r="S8">
-        <v>751.933959960938</v>
+        <v>764.709350585938</v>
       </c>
       <c r="T8">
-        <v>-1.40380859375</v>
+        <v>-2.1329345703125</v>
       </c>
       <c r="U8">
-        <v>-3.189697265625</v>
+        <v>-0.9749755859375</v>
       </c>
       <c r="V8">
-        <v>6.1458740234375</v>
+        <v>4.95208740234375</v>
       </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="1">
-        <v>46239</v>
+      <c r="A9" s="2">
+        <v>46253</v>
       </c>
       <c r="B9">
-        <v>10.5291137695313</v>
+        <v>-3.2568359375</v>
       </c>
       <c r="C9">
-        <v>15.4462890625</v>
+        <v>-1.51116943359375</v>
       </c>
       <c r="D9">
-        <v>11.3076171875</v>
+        <v>3.84210205078125</v>
       </c>
       <c r="E9">
-        <v>775.849975585938</v>
+        <v>770.359985351563</v>
       </c>
       <c r="F9">
-        <v>776.849975585938</v>
+        <v>772.469970703125</v>
       </c>
       <c r="G9">
-        <v>769.510009765625</v>
+        <v>768.099975585938</v>
       </c>
       <c r="H9">
-        <v>769.789978027344</v>
+        <v>769.059997558594</v>
       </c>
       <c r="I9">
-        <v>773.400085449219</v>
+        <v>771.677307128906</v>
       </c>
       <c r="J9">
-        <v>767.33056640625</v>
+        <v>767.074768066406</v>
       </c>
       <c r="K9">
-        <v>44689000</v>
+        <v>40306000</v>
       </c>
       <c r="L9">
-        <v>0.48096576333046</v>
+        <v>-0.199994772672653</v>
       </c>
       <c r="M9">
-        <v>60.1812019348145</v>
+        <v>49.4543342590332</v>
       </c>
       <c r="N9">
-        <v>15.1054992675781</v>
+        <v>16.0622634887695</v>
       </c>
       <c r="O9" t="s">
         <v>1</v>
       </c>
       <c r="P9">
-        <v>43.7006683349609</v>
+        <v>8.11643028259277</v>
       </c>
       <c r="Q9">
-        <v>764.792236328125</v>
+        <v>770.08544921875</v>
       </c>
       <c r="R9">
-        <v>755.466186523438</v>
+        <v>770.324523925781</v>
       </c>
       <c r="S9">
-        <v>749.989807128906</v>
+        <v>764.836547851563</v>
       </c>
       <c r="T9">
-        <v>-3.44989013671875</v>
+        <v>-0.79266357421875</v>
       </c>
       <c r="U9">
-        <v>-2.179443359375</v>
+        <v>-1.02520751953125</v>
       </c>
       <c r="V9">
-        <v>6.06951904296875</v>
+        <v>4.6025390625</v>
       </c>
     </row>
     <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="1">
-        <v>46238</v>
+      <c r="A10" s="2">
+        <v>46252</v>
       </c>
       <c r="B10">
-        <v>14.3104248046875</v>
+        <v>-3.63824462890625</v>
       </c>
       <c r="C10">
-        <v>12.27978515625</v>
+        <v>-0.693359375</v>
       </c>
       <c r="D10">
-        <v>6.887451171875</v>
+        <v>6.9818115234375</v>
       </c>
       <c r="E10">
-        <v>760.630004882813</v>
+        <v>768.700012207031</v>
       </c>
       <c r="F10">
-        <v>773.409973144531</v>
+        <v>769.5</v>
       </c>
       <c r="G10">
-        <v>760.52001953125</v>
+        <v>766.919982910156</v>
       </c>
       <c r="H10">
-        <v>771.330017089844</v>
+        <v>767.450012207031</v>
       </c>
       <c r="I10">
-        <v>772.6455078125</v>
+        <v>770.160522460938</v>
       </c>
       <c r="J10">
-        <v>764.456298828125</v>
+        <v>765.278137207031</v>
       </c>
       <c r="K10">
-        <v>69154704</v>
+        <v>43920900</v>
       </c>
       <c r="L10">
-        <v>0.650015711784363</v>
+        <v>-0.0433262400329113</v>
       </c>
       <c r="M10">
-        <v>52.2835159301758</v>
+        <v>42.6101760864258</v>
       </c>
       <c r="N10">
-        <v>-21.2984161376953</v>
+        <v>37.7328834533691</v>
       </c>
       <c r="O10" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P10">
-        <v>99.9999923706055</v>
+        <v>-37.4033470153809</v>
       </c>
       <c r="Q10">
-        <v>759.41162109375</v>
+        <v>770.899658203125</v>
       </c>
       <c r="R10">
-        <v>751.015747070313</v>
+        <v>770.637634277344</v>
       </c>
       <c r="S10">
-        <v>747.38720703125</v>
+        <v>764.214660644531</v>
       </c>
       <c r="T10">
-        <v>-0.76446533203125</v>
+        <v>0.6605224609375</v>
       </c>
       <c r="U10">
-        <v>3.936279296875</v>
+        <v>-1.641845703125</v>
       </c>
       <c r="V10">
-        <v>8.189208984375</v>
+        <v>4.88238525390625</v>
       </c>
     </row>
     <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="1">
-        <v>46237</v>
+      <c r="A11" s="2">
+        <v>46251</v>
       </c>
       <c r="B11">
-        <v>8.942138671875</v>
+        <v>-0.0660400390625</v>
       </c>
       <c r="C11">
-        <v>5.40350341796875</v>
+        <v>1.76776123046875</v>
       </c>
       <c r="D11">
-        <v>1.086669921875</v>
+        <v>10.3862915039063</v>
       </c>
       <c r="E11">
-        <v>749.440002441406</v>
+        <v>776.179992675781</v>
       </c>
       <c r="F11">
-        <v>758.580017089844</v>
+        <v>776.775024414063</v>
       </c>
       <c r="G11">
-        <v>748.799987792969</v>
+        <v>772.510009765625</v>
       </c>
       <c r="H11">
-        <v>757.669982910156</v>
+        <v>772.669982910156</v>
       </c>
       <c r="I11">
-        <v>759.710327148438</v>
+        <v>775.039672851563</v>
       </c>
       <c r="J11">
-        <v>752.819519042969</v>
+        <v>770.644836425781</v>
       </c>
       <c r="K11">
-        <v>59927500</v>
+        <v>34356500</v>
       </c>
       <c r="L11">
-        <v>0.261445552110672</v>
+        <v>-0.220467701554298</v>
       </c>
       <c r="M11">
-        <v>66.4326095581055</v>
+        <v>30.9368209838867</v>
       </c>
       <c r="N11">
-        <v>-12.6903162002563</v>
+        <v>-30.7619953155518</v>
       </c>
       <c r="O11" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P11">
-        <v>100</v>
+        <v>-23.7551555633545</v>
       </c>
       <c r="Q11">
-        <v>749.340942382813</v>
+        <v>774.1572265625</v>
       </c>
       <c r="R11">
-        <v>745.245666503906</v>
+        <v>771.646301269531</v>
       </c>
       <c r="S11">
-        <v>744.6484375</v>
+        <v>763.855163574219</v>
       </c>
       <c r="T11">
-        <v>1.13031005859375</v>
+        <v>-1.7353515625</v>
       </c>
       <c r="U11">
-        <v>4.01953125</v>
+        <v>-1.86517333984375</v>
       </c>
       <c r="V11">
-        <v>6.89080810546875</v>
+        <v>4.39483642578125</v>
       </c>
     </row>
     <row r="12" ht="19.5" customHeight="1">
-      <c r="A12" s="1">
-        <v>46234</v>
+      <c r="A12" s="2">
+        <v>46248</v>
       </c>
       <c r="B12">
-        <v>3.76422119140625</v>
+        <v>2.1373291015625</v>
       </c>
       <c r="C12">
-        <v>0.266845703125</v>
+        <v>4.10089111328125</v>
       </c>
       <c r="D12">
-        <v>-3.1119384765625</v>
+        <v>12.6900634765625</v>
       </c>
       <c r="E12">
-        <v>744.679992675781</v>
+        <v>778.539978027344</v>
       </c>
       <c r="F12">
-        <v>748.89501953125</v>
+        <v>778.799987792969</v>
       </c>
       <c r="G12">
-        <v>737.679992675781</v>
+        <v>775.430114746094</v>
       </c>
       <c r="H12">
-        <v>747.030029296875</v>
+        <v>776.340026855469</v>
       </c>
       <c r="I12">
-        <v>748.831909179688</v>
+        <v>778.64306640625</v>
       </c>
       <c r="J12">
-        <v>741.856079101563</v>
+        <v>774.530822753906</v>
       </c>
       <c r="K12">
-        <v>62445900</v>
+        <v>31367900</v>
       </c>
       <c r="L12">
-        <v>-0.255219966173172</v>
+        <v>0.00429280614480376</v>
       </c>
       <c r="M12">
-        <v>76.0884780883789</v>
+        <v>44.6818504333496</v>
       </c>
       <c r="N12">
-        <v>-3.3523223400116</v>
+        <v>6.78951740264893</v>
       </c>
       <c r="O12" t="s">
         <v>1</v>
       </c>
       <c r="P12">
-        <v>79.062629699707</v>
+        <v>6.06353616714478</v>
       </c>
       <c r="Q12">
-        <v>741.949462890625</v>
+        <v>775.51904296875</v>
       </c>
       <c r="R12">
-        <v>741.512023925781</v>
+        <v>771.248168945313</v>
       </c>
       <c r="S12">
-        <v>743.095886230469</v>
+        <v>762.794372558594</v>
       </c>
       <c r="T12">
-        <v>-0.0631103515625</v>
+        <v>-0.15692138671875</v>
       </c>
       <c r="U12">
-        <v>4.17608642578125</v>
+        <v>-0.8992919921875</v>
       </c>
       <c r="V12">
-        <v>6.975830078125</v>
+        <v>4.11224365234375</v>
       </c>
     </row>
     <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="1">
-        <v>46233</v>
+      <c r="A13" s="2">
+        <v>46247</v>
       </c>
       <c r="B13">
-        <v>0.3529052734375</v>
+        <v>2.138427734375</v>
       </c>
       <c r="C13">
-        <v>-2.81561279296875</v>
+        <v>5.8125</v>
       </c>
       <c r="D13">
-        <v>-5.63934326171875</v>
+        <v>13.65576171875</v>
       </c>
       <c r="E13">
-        <v>736.049987792969</v>
+        <v>774.869995117188</v>
       </c>
       <c r="F13">
-        <v>742.450012207031</v>
+        <v>779.369995117188</v>
       </c>
       <c r="G13">
-        <v>734.590026855469</v>
+        <v>774.111022949219</v>
       </c>
       <c r="H13">
-        <v>741.690002441406</v>
+        <v>777.880004882813</v>
       </c>
       <c r="I13">
-        <v>745.024169921875</v>
+        <v>779.426086425781</v>
       </c>
       <c r="J13">
-        <v>735.741333007813</v>
+        <v>774.595520019531</v>
       </c>
       <c r="K13">
-        <v>66811200</v>
+        <v>35634400</v>
       </c>
       <c r="L13">
-        <v>-0.330935537815094</v>
+        <v>0.0119076687842607</v>
       </c>
       <c r="M13">
-        <v>78.7276840209961</v>
+        <v>41.8410453796387</v>
       </c>
       <c r="N13">
-        <v>-14.5367441177368</v>
+        <v>-30.5117282867432</v>
       </c>
       <c r="O13" t="s">
         <v>1</v>
       </c>
       <c r="P13">
-        <v>32.4318542480469</v>
+        <v>25.7974395751953</v>
       </c>
       <c r="Q13">
-        <v>737.999877929688</v>
+        <v>774.528503417969</v>
       </c>
       <c r="R13">
-        <v>739.99853515625</v>
+        <v>769.578063964844</v>
       </c>
       <c r="S13">
-        <v>742.720581054688</v>
+        <v>761.106079101563</v>
       </c>
       <c r="T13">
-        <v>2.57415771484375</v>
+        <v>0.05609130859375</v>
       </c>
       <c r="U13">
-        <v>1.15130615234375</v>
+        <v>0.4844970703125</v>
       </c>
       <c r="V13">
-        <v>9.2828369140625</v>
+        <v>4.83056640625</v>
       </c>
     </row>
     <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="1">
-        <v>46232</v>
+      <c r="A14" s="2">
+        <v>46246</v>
       </c>
       <c r="B14">
-        <v>-3.86669921875</v>
+        <v>0.5604248046875</v>
       </c>
       <c r="C14">
-        <v>-5.0338134765625</v>
+        <v>6.97613525390625</v>
       </c>
       <c r="D14">
-        <v>-6.51739501953125</v>
+        <v>14.05029296875</v>
       </c>
       <c r="E14">
-        <v>739.969970703125</v>
+        <v>774.710021972656</v>
       </c>
       <c r="F14">
-        <v>742.679992675781</v>
+        <v>774.900024414063</v>
       </c>
       <c r="G14">
-        <v>729.099975585938</v>
+        <v>771.280029296875</v>
       </c>
       <c r="H14">
-        <v>729.460021972656</v>
+        <v>772.489990234375</v>
       </c>
       <c r="I14">
-        <v>734.330322265625</v>
+        <v>774.973022460938</v>
       </c>
       <c r="J14">
-        <v>726.553405761719</v>
+        <v>770.355773925781</v>
       </c>
       <c r="K14">
-        <v>70697200</v>
+        <v>33179100</v>
       </c>
       <c r="L14">
-        <v>-0.33855327963829</v>
+        <v>-0.104282923042774</v>
       </c>
       <c r="M14">
-        <v>92.1187515258789</v>
+        <v>60.2131042480469</v>
       </c>
       <c r="N14">
-        <v>24.4579162597656</v>
+        <v>1.56267952919006</v>
       </c>
       <c r="O14" t="s">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>3.13029456138611</v>
+      </c>
+      <c r="Q14">
+        <v>771.74609375</v>
+      </c>
+      <c r="R14">
+        <v>767.270751953125</v>
+      </c>
+      <c r="S14">
+        <v>759.28759765625</v>
+      </c>
+      <c r="T14">
+        <v>0.072998046875</v>
+      </c>
+      <c r="U14">
+        <v>-0.92425537109375</v>
+      </c>
+      <c r="V14">
+        <v>4.61724853515625</v>
+      </c>
+    </row>
+    <row r="15" ht="19.5" customHeight="1">
+      <c r="A15" s="2">
+        <v>46245</v>
+      </c>
+      <c r="B15">
+        <v>0.1639404296875</v>
+      </c>
+      <c r="C15">
+        <v>10.3299560546875</v>
+      </c>
+      <c r="D15">
+        <v>14.33642578125</v>
+      </c>
+      <c r="E15">
+        <v>774.530029296875</v>
+      </c>
+      <c r="F15">
+        <v>774.609985351563</v>
+      </c>
+      <c r="G15">
+        <v>769.200012207031</v>
+      </c>
+      <c r="H15">
+        <v>770.559997558594</v>
+      </c>
+      <c r="I15">
+        <v>772.776306152344</v>
+      </c>
+      <c r="J15">
+        <v>768.681701660156</v>
+      </c>
+      <c r="K15">
+        <v>36740500</v>
+      </c>
+      <c r="L15">
+        <v>0.0452444888651371</v>
+      </c>
+      <c r="M15">
+        <v>59.2866439819336</v>
+      </c>
+      <c r="N15">
+        <v>5.286705493927</v>
+      </c>
+      <c r="O15" t="s">
         <v>23</v>
       </c>
-      <c r="P14">
-        <v>-85.4580154418945</v>
-      </c>
-      <c r="Q14">
-        <v>735.184448242188</v>
-      </c>
-      <c r="R14">
-        <v>739.921020507813</v>
-      </c>
-      <c r="S14">
-        <v>743.067321777344</v>
-      </c>
-      <c r="T14">
-        <v>-8.34967041015625</v>
-      </c>
-      <c r="U14">
-        <v>-2.54656982421875</v>
-      </c>
-      <c r="V14">
-        <v>7.77691650390625</v>
-      </c>
-    </row>
-    <row r="15" ht="19.5" customHeight="1">
-      <c r="A15" s="1">
-        <v>46231</v>
-      </c>
-      <c r="B15">
-        <v>-0.8109130859375</v>
-      </c>
-      <c r="C15">
-        <v>-3.56964111328125</v>
-      </c>
-      <c r="D15">
-        <v>-4.41912841796875</v>
-      </c>
-      <c r="E15">
-        <v>739.190002441406</v>
-      </c>
-      <c r="F15">
-        <v>742.790100097656</v>
-      </c>
-      <c r="G15">
-        <v>735.97998046875</v>
-      </c>
-      <c r="H15">
-        <v>740.859985351563</v>
-      </c>
-      <c r="I15">
-        <v>743.945617675781</v>
-      </c>
-      <c r="J15">
-        <v>736.403442382813</v>
-      </c>
-      <c r="K15">
-        <v>47322200</v>
-      </c>
-      <c r="L15">
-        <v>0.374776214361191</v>
-      </c>
-      <c r="M15">
-        <v>74.015983581543</v>
-      </c>
-      <c r="N15">
-        <v>5.70302963256836</v>
-      </c>
-      <c r="O15" t="s">
-        <v>1</v>
-      </c>
       <c r="P15">
-        <v>29.2502498626709</v>
+        <v>-12.588695526123</v>
       </c>
       <c r="Q15">
-        <v>740.251586914063</v>
+        <v>770.895874023438</v>
       </c>
       <c r="R15">
-        <v>742.542541503906</v>
+        <v>765.665771484375</v>
       </c>
       <c r="S15">
-        <v>744.463928222656</v>
+        <v>757.667053222656</v>
       </c>
       <c r="T15">
-        <v>1.155517578125</v>
+        <v>-1.83367919921875</v>
       </c>
       <c r="U15">
-        <v>0.4234619140625</v>
+        <v>-0.518310546875</v>
       </c>
       <c r="V15">
-        <v>7.54217529296875</v>
+        <v>4.0946044921875</v>
       </c>
     </row>
     <row r="16" ht="19.5" customHeight="1">
-      <c r="A16" s="1">
-        <v>46230</v>
+      <c r="A16" s="2">
+        <v>46244</v>
       </c>
       <c r="B16">
-        <v>-2.93133544921875</v>
+        <v>1.07012939453125</v>
       </c>
       <c r="C16">
-        <v>-4.898193359375</v>
+        <v>12.7230834960938</v>
       </c>
       <c r="D16">
-        <v>-4.6815185546875</v>
+        <v>14.5609741210938</v>
       </c>
       <c r="E16">
-        <v>744.909973144531</v>
+        <v>772.599975585938</v>
       </c>
       <c r="F16">
-        <v>745.530029296875</v>
+        <v>775.049987792969</v>
       </c>
       <c r="G16">
-        <v>735.869995117188</v>
+        <v>771.619995117188</v>
       </c>
       <c r="H16">
-        <v>739.090026855469</v>
+        <v>773.030029296875</v>
       </c>
       <c r="I16">
-        <v>742.739501953125</v>
+        <v>774.887023925781</v>
       </c>
       <c r="J16">
-        <v>735.81982421875</v>
+        <v>771.254333496094</v>
       </c>
       <c r="K16">
-        <v>41461100</v>
+        <v>39249400</v>
       </c>
       <c r="L16">
-        <v>0.297156929969788</v>
+        <v>0.0771513432264328</v>
       </c>
       <c r="M16">
-        <v>70.022575378418</v>
+        <v>56.3097152709961</v>
       </c>
       <c r="N16">
-        <v>20.963960647583</v>
+        <v>0.722540974617004</v>
       </c>
       <c r="O16" t="s">
         <v>1</v>
       </c>
       <c r="P16">
-        <v>17.5370769500732</v>
+        <v>11.3912715911865</v>
       </c>
       <c r="Q16">
-        <v>740.098510742188</v>
+        <v>771.117980957031</v>
       </c>
       <c r="R16">
-        <v>742.947082519531</v>
+        <v>764.006713867188</v>
       </c>
       <c r="S16">
-        <v>744.827575683594</v>
+        <v>756.085510253906</v>
       </c>
       <c r="T16">
-        <v>-2.79052734375</v>
+        <v>-0.1629638671875</v>
       </c>
       <c r="U16">
-        <v>-0.0501708984375</v>
+        <v>-0.36566162109375</v>
       </c>
       <c r="V16">
-        <v>6.919677734375</v>
+        <v>3.6326904296875</v>
       </c>
     </row>
     <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="1">
-        <v>46227</v>
+      <c r="A17" s="2">
+        <v>46241</v>
       </c>
       <c r="B17">
-        <v>-3.06939697265625</v>
+        <v>2.55120849609375</v>
       </c>
       <c r="C17">
-        <v>-4.58935546875</v>
+        <v>13.9462890625</v>
       </c>
       <c r="D17">
-        <v>-4.2686767578125</v>
+        <v>14.0487060546875</v>
       </c>
       <c r="E17">
-        <v>738.510009765625</v>
+        <v>771.02001953125</v>
       </c>
       <c r="F17">
-        <v>743.719970703125</v>
+        <v>773.914978027344</v>
       </c>
       <c r="G17">
-        <v>737.289978027344</v>
+        <v>769.609985351563</v>
       </c>
       <c r="H17">
-        <v>738.929992675781</v>
+        <v>773.260009765625</v>
       </c>
       <c r="I17">
-        <v>742.815734863281</v>
+        <v>774.138610839844</v>
       </c>
       <c r="J17">
-        <v>736.110717773438</v>
+        <v>768.873413085938</v>
       </c>
       <c r="K17">
-        <v>44781900</v>
+        <v>43586300</v>
       </c>
       <c r="L17">
-        <v>0.354774117469788</v>
+        <v>0.194768995046616</v>
       </c>
       <c r="M17">
-        <v>57.8871383666992</v>
+        <v>55.9057731628418</v>
       </c>
       <c r="N17">
-        <v>9.43521308898926</v>
+        <v>-0.691173672676086</v>
       </c>
       <c r="O17" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P17">
-        <v>-15.6245880126953</v>
+        <v>3.94128084182739</v>
       </c>
       <c r="Q17">
-        <v>740.985229492188</v>
+        <v>769.178833007813</v>
       </c>
       <c r="R17">
-        <v>744.20166015625</v>
+        <v>761.331909179688</v>
       </c>
       <c r="S17">
-        <v>745.505920410156</v>
+        <v>754.049072265625</v>
       </c>
       <c r="T17">
-        <v>-0.90423583984375</v>
+        <v>0.2236328125</v>
       </c>
       <c r="U17">
-        <v>-1.17926025390625</v>
+        <v>-0.736572265625</v>
       </c>
       <c r="V17">
-        <v>6.70501708984375</v>
+        <v>5.26519775390625</v>
       </c>
     </row>
     <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="1">
-        <v>46226</v>
+      <c r="A18" s="2">
+        <v>46240</v>
       </c>
       <c r="B18">
-        <v>-2.6964111328125</v>
+        <v>4.96710205078125</v>
       </c>
       <c r="C18">
-        <v>-4.32305908203125</v>
+        <v>14.4755249023438</v>
       </c>
       <c r="D18">
-        <v>-3.09246826171875</v>
+        <v>12.9638061523438</v>
       </c>
       <c r="E18">
-        <v>739.369995117188</v>
+        <v>770.210021972656</v>
       </c>
       <c r="F18">
-        <v>742.559997558594</v>
+        <v>771.820007324219</v>
       </c>
       <c r="G18">
-        <v>735.210021972656</v>
+        <v>767.460021972656</v>
       </c>
       <c r="H18">
-        <v>738.179992675781</v>
+        <v>768.559997558594</v>
       </c>
       <c r="I18">
-        <v>740.84423828125</v>
+        <v>770.416198730469</v>
       </c>
       <c r="J18">
-        <v>734.918212890625</v>
+        <v>764.270324707031</v>
       </c>
       <c r="K18">
-        <v>55437300</v>
+        <v>38416800</v>
       </c>
       <c r="L18">
-        <v>0.242870509624481</v>
+        <v>0.29572406411171</v>
       </c>
       <c r="M18">
-        <v>52.8962631225586</v>
+        <v>56.2948684692383</v>
       </c>
       <c r="N18">
-        <v>10.7656211853027</v>
+        <v>-6.45771980285645</v>
       </c>
       <c r="O18" t="s">
         <v>23</v>
       </c>
       <c r="P18">
-        <v>-89.2781143188477</v>
+        <v>-21.9880218505859</v>
       </c>
       <c r="Q18">
-        <v>742.681640625</v>
+        <v>766.265747070313</v>
       </c>
       <c r="R18">
-        <v>745.701232910156</v>
+        <v>758.244384765625</v>
       </c>
       <c r="S18">
-        <v>746.256774902344</v>
+        <v>751.933959960938</v>
       </c>
       <c r="T18">
-        <v>-1.71575927734375</v>
+        <v>-1.40380859375</v>
       </c>
       <c r="U18">
-        <v>-0.29180908203125</v>
+        <v>-3.189697265625</v>
       </c>
       <c r="V18">
-        <v>5.926025390625</v>
+        <v>6.1458740234375</v>
       </c>
     </row>
     <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="1">
-        <v>46225</v>
+      <c r="A19" s="2">
+        <v>46239</v>
       </c>
       <c r="B19">
-        <v>1.14031982421875</v>
+        <v>10.5291137695313</v>
       </c>
       <c r="C19">
-        <v>-1.9736328125</v>
+        <v>15.4462890625</v>
       </c>
       <c r="D19">
-        <v>-0.88818359375</v>
+        <v>11.3076171875</v>
       </c>
       <c r="E19">
-        <v>746.619995117188</v>
+        <v>775.849975585938</v>
       </c>
       <c r="F19">
-        <v>750.02001953125</v>
+        <v>776.849975585938</v>
       </c>
       <c r="G19">
-        <v>746.369995117188</v>
+        <v>769.510009765625</v>
       </c>
       <c r="H19">
-        <v>747.409973144531</v>
+        <v>769.789978027344</v>
       </c>
       <c r="I19">
-        <v>749.90087890625</v>
+        <v>773.400085449219</v>
       </c>
       <c r="J19">
-        <v>745.880249023438</v>
+        <v>767.33056640625</v>
       </c>
       <c r="K19">
-        <v>32836200</v>
+        <v>44689000</v>
       </c>
       <c r="L19">
-        <v>0.288585841655731</v>
+        <v>0.48096576333046</v>
       </c>
       <c r="M19">
-        <v>47.755126953125</v>
+        <v>60.1812019348145</v>
       </c>
       <c r="N19">
-        <v>-9.10026931762695</v>
+        <v>15.1054992675781</v>
       </c>
       <c r="O19" t="s">
         <v>1</v>
       </c>
       <c r="P19">
-        <v>18.1666526794434</v>
+        <v>43.7006683349609</v>
       </c>
       <c r="Q19">
-        <v>747.375854492188</v>
+        <v>764.792236328125</v>
       </c>
       <c r="R19">
-        <v>747.846984863281</v>
+        <v>755.466186523438</v>
       </c>
       <c r="S19">
-        <v>747.18115234375</v>
+        <v>749.989807128906</v>
       </c>
       <c r="T19">
-        <v>-0.119140625</v>
+        <v>-3.44989013671875</v>
       </c>
       <c r="U19">
-        <v>-0.48974609375</v>
+        <v>-2.179443359375</v>
       </c>
       <c r="V19">
-        <v>4.0206298828125</v>
+        <v>6.06951904296875</v>
       </c>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="1">
-        <v>46224</v>
+      <c r="A20" s="2">
+        <v>46238</v>
       </c>
       <c r="B20">
-        <v>-0.80126953125</v>
+        <v>14.3104248046875</v>
       </c>
       <c r="C20">
-        <v>-2.4951171875</v>
+        <v>12.27978515625</v>
       </c>
       <c r="D20">
-        <v>-1.24127197265625</v>
+        <v>6.887451171875</v>
       </c>
       <c r="E20">
-        <v>746.289978027344</v>
+        <v>760.630004882813</v>
       </c>
       <c r="F20">
-        <v>749.039978027344</v>
+        <v>773.409973144531</v>
       </c>
       <c r="G20">
-        <v>744.179992675781</v>
+        <v>760.52001953125</v>
       </c>
       <c r="H20">
-        <v>748.280029296875</v>
+        <v>771.330017089844</v>
       </c>
       <c r="I20">
-        <v>751.154418945313</v>
+        <v>772.6455078125</v>
       </c>
       <c r="J20">
-        <v>745.55029296875</v>
+        <v>764.456298828125</v>
       </c>
       <c r="K20">
-        <v>34324200</v>
+        <v>69154704</v>
       </c>
       <c r="L20">
-        <v>0.0933489128947258</v>
+        <v>0.650015711784363</v>
       </c>
       <c r="M20">
-        <v>52.5360488891602</v>
+        <v>52.2835159301758</v>
       </c>
       <c r="N20">
-        <v>-2.84704780578613</v>
+        <v>-21.2984161376953</v>
       </c>
       <c r="O20" t="s">
         <v>1</v>
       </c>
       <c r="P20">
+        <v>99.9999923706055</v>
+      </c>
+      <c r="Q20">
+        <v>759.41162109375</v>
+      </c>
+      <c r="R20">
+        <v>751.015747070313</v>
+      </c>
+      <c r="S20">
+        <v>747.38720703125</v>
+      </c>
+      <c r="T20">
+        <v>-0.76446533203125</v>
+      </c>
+      <c r="U20">
+        <v>3.936279296875</v>
+      </c>
+      <c r="V20">
+        <v>8.189208984375</v>
+      </c>
+    </row>
+    <row r="21" ht="19.5" customHeight="1">
+      <c r="A21" s="2">
+        <v>46237</v>
+      </c>
+      <c r="B21">
+        <v>8.942138671875</v>
+      </c>
+      <c r="C21">
+        <v>5.40350341796875</v>
+      </c>
+      <c r="D21">
+        <v>1.086669921875</v>
+      </c>
+      <c r="E21">
+        <v>749.440002441406</v>
+      </c>
+      <c r="F21">
+        <v>758.580017089844</v>
+      </c>
+      <c r="G21">
+        <v>748.799987792969</v>
+      </c>
+      <c r="H21">
+        <v>757.669982910156</v>
+      </c>
+      <c r="I21">
+        <v>759.710327148438</v>
+      </c>
+      <c r="J21">
+        <v>752.819519042969</v>
+      </c>
+      <c r="K21">
+        <v>59927500</v>
+      </c>
+      <c r="L21">
+        <v>0.261445552110672</v>
+      </c>
+      <c r="M21">
+        <v>66.4326095581055</v>
+      </c>
+      <c r="N21">
+        <v>-12.6903162002563</v>
+      </c>
+      <c r="O21" t="s">
+        <v>1</v>
+      </c>
+      <c r="P21">
+        <v>100</v>
+      </c>
+      <c r="Q21">
+        <v>749.340942382813</v>
+      </c>
+      <c r="R21">
+        <v>745.245666503906</v>
+      </c>
+      <c r="S21">
+        <v>744.6484375</v>
+      </c>
+      <c r="T21">
+        <v>1.13031005859375</v>
+      </c>
+      <c r="U21">
+        <v>4.01953125</v>
+      </c>
+      <c r="V21">
+        <v>6.89080810546875</v>
+      </c>
+    </row>
+    <row r="22" ht="19.5" customHeight="1">
+      <c r="A22" s="2">
+        <v>46234</v>
+      </c>
+      <c r="B22">
+        <v>3.76422119140625</v>
+      </c>
+      <c r="C22">
+        <v>0.266845703125</v>
+      </c>
+      <c r="D22">
+        <v>-3.1119384765625</v>
+      </c>
+      <c r="E22">
+        <v>744.679992675781</v>
+      </c>
+      <c r="F22">
+        <v>748.89501953125</v>
+      </c>
+      <c r="G22">
+        <v>737.679992675781</v>
+      </c>
+      <c r="H22">
+        <v>747.030029296875</v>
+      </c>
+      <c r="I22">
+        <v>748.831909179688</v>
+      </c>
+      <c r="J22">
+        <v>741.856079101563</v>
+      </c>
+      <c r="K22">
+        <v>62445900</v>
+      </c>
+      <c r="L22">
+        <v>-0.255219966173172</v>
+      </c>
+      <c r="M22">
+        <v>76.0884780883789</v>
+      </c>
+      <c r="N22">
+        <v>-3.3523223400116</v>
+      </c>
+      <c r="O22" t="s">
+        <v>1</v>
+      </c>
+      <c r="P22">
+        <v>79.062629699707</v>
+      </c>
+      <c r="Q22">
+        <v>741.949462890625</v>
+      </c>
+      <c r="R22">
+        <v>741.512023925781</v>
+      </c>
+      <c r="S22">
+        <v>743.095886230469</v>
+      </c>
+      <c r="T22">
+        <v>-0.0631103515625</v>
+      </c>
+      <c r="U22">
+        <v>4.17608642578125</v>
+      </c>
+      <c r="V22">
+        <v>6.975830078125</v>
+      </c>
+    </row>
+    <row r="23" ht="19.5" customHeight="1">
+      <c r="A23" s="2">
+        <v>46233</v>
+      </c>
+      <c r="B23">
+        <v>0.3529052734375</v>
+      </c>
+      <c r="C23">
+        <v>-2.81561279296875</v>
+      </c>
+      <c r="D23">
+        <v>-5.63934326171875</v>
+      </c>
+      <c r="E23">
+        <v>736.049987792969</v>
+      </c>
+      <c r="F23">
+        <v>742.450012207031</v>
+      </c>
+      <c r="G23">
+        <v>734.590026855469</v>
+      </c>
+      <c r="H23">
+        <v>741.690002441406</v>
+      </c>
+      <c r="I23">
+        <v>745.024169921875</v>
+      </c>
+      <c r="J23">
+        <v>735.741333007813</v>
+      </c>
+      <c r="K23">
+        <v>66811200</v>
+      </c>
+      <c r="L23">
+        <v>-0.330935537815094</v>
+      </c>
+      <c r="M23">
+        <v>78.7276840209961</v>
+      </c>
+      <c r="N23">
+        <v>-14.5367441177368</v>
+      </c>
+      <c r="O23" t="s">
+        <v>1</v>
+      </c>
+      <c r="P23">
+        <v>32.4318542480469</v>
+      </c>
+      <c r="Q23">
+        <v>737.999877929688</v>
+      </c>
+      <c r="R23">
+        <v>739.99853515625</v>
+      </c>
+      <c r="S23">
+        <v>742.720581054688</v>
+      </c>
+      <c r="T23">
+        <v>2.57415771484375</v>
+      </c>
+      <c r="U23">
+        <v>1.15130615234375</v>
+      </c>
+      <c r="V23">
+        <v>9.2828369140625</v>
+      </c>
+    </row>
+    <row r="24" ht="19.5" customHeight="1">
+      <c r="A24" s="2">
+        <v>46232</v>
+      </c>
+      <c r="B24">
+        <v>-3.86669921875</v>
+      </c>
+      <c r="C24">
+        <v>-5.0338134765625</v>
+      </c>
+      <c r="D24">
+        <v>-6.51739501953125</v>
+      </c>
+      <c r="E24">
+        <v>739.969970703125</v>
+      </c>
+      <c r="F24">
+        <v>742.679992675781</v>
+      </c>
+      <c r="G24">
+        <v>729.099975585938</v>
+      </c>
+      <c r="H24">
+        <v>729.460021972656</v>
+      </c>
+      <c r="I24">
+        <v>734.330322265625</v>
+      </c>
+      <c r="J24">
+        <v>726.553405761719</v>
+      </c>
+      <c r="K24">
+        <v>70697200</v>
+      </c>
+      <c r="L24">
+        <v>-0.33855327963829</v>
+      </c>
+      <c r="M24">
+        <v>92.1187515258789</v>
+      </c>
+      <c r="N24">
+        <v>24.4579162597656</v>
+      </c>
+      <c r="O24" t="s">
+        <v>23</v>
+      </c>
+      <c r="P24">
+        <v>-85.4580154418945</v>
+      </c>
+      <c r="Q24">
+        <v>735.184448242188</v>
+      </c>
+      <c r="R24">
+        <v>739.921020507813</v>
+      </c>
+      <c r="S24">
+        <v>743.067321777344</v>
+      </c>
+      <c r="T24">
+        <v>-8.34967041015625</v>
+      </c>
+      <c r="U24">
+        <v>-2.54656982421875</v>
+      </c>
+      <c r="V24">
+        <v>7.77691650390625</v>
+      </c>
+    </row>
+    <row r="25" ht="19.5" customHeight="1">
+      <c r="A25" s="2">
+        <v>46231</v>
+      </c>
+      <c r="B25">
+        <v>-0.8109130859375</v>
+      </c>
+      <c r="C25">
+        <v>-3.56964111328125</v>
+      </c>
+      <c r="D25">
+        <v>-4.41912841796875</v>
+      </c>
+      <c r="E25">
+        <v>739.190002441406</v>
+      </c>
+      <c r="F25">
+        <v>742.790100097656</v>
+      </c>
+      <c r="G25">
+        <v>735.97998046875</v>
+      </c>
+      <c r="H25">
+        <v>740.859985351563</v>
+      </c>
+      <c r="I25">
+        <v>743.945617675781</v>
+      </c>
+      <c r="J25">
+        <v>736.403442382813</v>
+      </c>
+      <c r="K25">
+        <v>47322200</v>
+      </c>
+      <c r="L25">
+        <v>0.374776214361191</v>
+      </c>
+      <c r="M25">
+        <v>74.015983581543</v>
+      </c>
+      <c r="N25">
+        <v>5.70302963256836</v>
+      </c>
+      <c r="O25" t="s">
+        <v>1</v>
+      </c>
+      <c r="P25">
+        <v>29.2502498626709</v>
+      </c>
+      <c r="Q25">
+        <v>740.251586914063</v>
+      </c>
+      <c r="R25">
+        <v>742.542541503906</v>
+      </c>
+      <c r="S25">
+        <v>744.463928222656</v>
+      </c>
+      <c r="T25">
+        <v>1.155517578125</v>
+      </c>
+      <c r="U25">
+        <v>0.4234619140625</v>
+      </c>
+      <c r="V25">
+        <v>7.54217529296875</v>
+      </c>
+    </row>
+    <row r="26" ht="19.5" customHeight="1">
+      <c r="A26" s="2">
+        <v>46230</v>
+      </c>
+      <c r="B26">
+        <v>-2.93133544921875</v>
+      </c>
+      <c r="C26">
+        <v>-4.898193359375</v>
+      </c>
+      <c r="D26">
+        <v>-4.6815185546875</v>
+      </c>
+      <c r="E26">
+        <v>744.909973144531</v>
+      </c>
+      <c r="F26">
+        <v>745.530029296875</v>
+      </c>
+      <c r="G26">
+        <v>735.869995117188</v>
+      </c>
+      <c r="H26">
+        <v>739.090026855469</v>
+      </c>
+      <c r="I26">
+        <v>742.739501953125</v>
+      </c>
+      <c r="J26">
+        <v>735.81982421875</v>
+      </c>
+      <c r="K26">
+        <v>41461100</v>
+      </c>
+      <c r="L26">
+        <v>0.297156929969788</v>
+      </c>
+      <c r="M26">
+        <v>70.022575378418</v>
+      </c>
+      <c r="N26">
+        <v>20.963960647583</v>
+      </c>
+      <c r="O26" t="s">
+        <v>1</v>
+      </c>
+      <c r="P26">
+        <v>17.5370769500732</v>
+      </c>
+      <c r="Q26">
+        <v>740.098510742188</v>
+      </c>
+      <c r="R26">
+        <v>742.947082519531</v>
+      </c>
+      <c r="S26">
+        <v>744.827575683594</v>
+      </c>
+      <c r="T26">
+        <v>-2.79052734375</v>
+      </c>
+      <c r="U26">
+        <v>-0.0501708984375</v>
+      </c>
+      <c r="V26">
+        <v>6.919677734375</v>
+      </c>
+    </row>
+    <row r="27" ht="19.5" customHeight="1">
+      <c r="A27" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B27">
+        <v>-3.06939697265625</v>
+      </c>
+      <c r="C27">
+        <v>-4.58935546875</v>
+      </c>
+      <c r="D27">
+        <v>-4.2686767578125</v>
+      </c>
+      <c r="E27">
+        <v>738.510009765625</v>
+      </c>
+      <c r="F27">
+        <v>743.719970703125</v>
+      </c>
+      <c r="G27">
+        <v>737.289978027344</v>
+      </c>
+      <c r="H27">
+        <v>738.929992675781</v>
+      </c>
+      <c r="I27">
+        <v>742.815734863281</v>
+      </c>
+      <c r="J27">
+        <v>736.110717773438</v>
+      </c>
+      <c r="K27">
+        <v>44781900</v>
+      </c>
+      <c r="L27">
+        <v>0.354774117469788</v>
+      </c>
+      <c r="M27">
+        <v>57.8871383666992</v>
+      </c>
+      <c r="N27">
+        <v>9.43521308898926</v>
+      </c>
+      <c r="O27" t="s">
+        <v>23</v>
+      </c>
+      <c r="P27">
+        <v>-15.6245880126953</v>
+      </c>
+      <c r="Q27">
+        <v>740.985229492188</v>
+      </c>
+      <c r="R27">
+        <v>744.20166015625</v>
+      </c>
+      <c r="S27">
+        <v>745.505920410156</v>
+      </c>
+      <c r="T27">
+        <v>-0.90423583984375</v>
+      </c>
+      <c r="U27">
+        <v>-1.17926025390625</v>
+      </c>
+      <c r="V27">
+        <v>6.70501708984375</v>
+      </c>
+    </row>
+    <row r="28" ht="19.5" customHeight="1">
+      <c r="A28" s="2">
+        <v>46226</v>
+      </c>
+      <c r="B28">
+        <v>-2.6964111328125</v>
+      </c>
+      <c r="C28">
+        <v>-4.32305908203125</v>
+      </c>
+      <c r="D28">
+        <v>-3.09246826171875</v>
+      </c>
+      <c r="E28">
+        <v>739.369995117188</v>
+      </c>
+      <c r="F28">
+        <v>742.559997558594</v>
+      </c>
+      <c r="G28">
+        <v>735.210021972656</v>
+      </c>
+      <c r="H28">
+        <v>738.179992675781</v>
+      </c>
+      <c r="I28">
+        <v>740.84423828125</v>
+      </c>
+      <c r="J28">
+        <v>734.918212890625</v>
+      </c>
+      <c r="K28">
+        <v>55437300</v>
+      </c>
+      <c r="L28">
+        <v>0.242870509624481</v>
+      </c>
+      <c r="M28">
+        <v>52.8962631225586</v>
+      </c>
+      <c r="N28">
+        <v>10.7656211853027</v>
+      </c>
+      <c r="O28" t="s">
+        <v>23</v>
+      </c>
+      <c r="P28">
+        <v>-89.2781143188477</v>
+      </c>
+      <c r="Q28">
+        <v>742.681640625</v>
+      </c>
+      <c r="R28">
+        <v>745.701232910156</v>
+      </c>
+      <c r="S28">
+        <v>746.256774902344</v>
+      </c>
+      <c r="T28">
+        <v>-1.71575927734375</v>
+      </c>
+      <c r="U28">
+        <v>-0.29180908203125</v>
+      </c>
+      <c r="V28">
+        <v>5.926025390625</v>
+      </c>
+    </row>
+    <row r="29" ht="19.5" customHeight="1">
+      <c r="A29" s="2">
+        <v>46225</v>
+      </c>
+      <c r="B29">
+        <v>1.14031982421875</v>
+      </c>
+      <c r="C29">
+        <v>-1.9736328125</v>
+      </c>
+      <c r="D29">
+        <v>-0.88818359375</v>
+      </c>
+      <c r="E29">
+        <v>746.619995117188</v>
+      </c>
+      <c r="F29">
+        <v>750.02001953125</v>
+      </c>
+      <c r="G29">
+        <v>746.369995117188</v>
+      </c>
+      <c r="H29">
+        <v>747.409973144531</v>
+      </c>
+      <c r="I29">
+        <v>749.90087890625</v>
+      </c>
+      <c r="J29">
+        <v>745.880249023438</v>
+      </c>
+      <c r="K29">
+        <v>32836200</v>
+      </c>
+      <c r="L29">
+        <v>0.288585841655731</v>
+      </c>
+      <c r="M29">
+        <v>47.755126953125</v>
+      </c>
+      <c r="N29">
+        <v>-9.10026931762695</v>
+      </c>
+      <c r="O29" t="s">
+        <v>1</v>
+      </c>
+      <c r="P29">
+        <v>18.1666526794434</v>
+      </c>
+      <c r="Q29">
+        <v>747.375854492188</v>
+      </c>
+      <c r="R29">
+        <v>747.846984863281</v>
+      </c>
+      <c r="S29">
+        <v>747.18115234375</v>
+      </c>
+      <c r="T29">
+        <v>-0.119140625</v>
+      </c>
+      <c r="U29">
+        <v>-0.48974609375</v>
+      </c>
+      <c r="V29">
+        <v>4.0206298828125</v>
+      </c>
+    </row>
+    <row r="30" ht="19.5" customHeight="1">
+      <c r="A30" s="2">
+        <v>46224</v>
+      </c>
+      <c r="B30">
+        <v>-0.80126953125</v>
+      </c>
+      <c r="C30">
+        <v>-2.4951171875</v>
+      </c>
+      <c r="D30">
+        <v>-1.24127197265625</v>
+      </c>
+      <c r="E30">
+        <v>746.289978027344</v>
+      </c>
+      <c r="F30">
+        <v>749.039978027344</v>
+      </c>
+      <c r="G30">
+        <v>744.179992675781</v>
+      </c>
+      <c r="H30">
+        <v>748.280029296875</v>
+      </c>
+      <c r="I30">
+        <v>751.154418945313</v>
+      </c>
+      <c r="J30">
+        <v>745.55029296875</v>
+      </c>
+      <c r="K30">
+        <v>34324200</v>
+      </c>
+      <c r="L30">
+        <v>0.0933489128947258</v>
+      </c>
+      <c r="M30">
+        <v>52.5360488891602</v>
+      </c>
+      <c r="N30">
+        <v>-2.84704780578613</v>
+      </c>
+      <c r="O30" t="s">
+        <v>1</v>
+      </c>
+      <c r="P30">
         <v>29.6290588378906</v>
       </c>
-      <c r="Q20">
+      <c r="Q30">
         <v>747.024291992188</v>
       </c>
-      <c r="R20">
+      <c r="R30">
         <v>747.635925292969</v>
       </c>
-      <c r="S20">
+      <c r="S30">
         <v>746.969909667969</v>
       </c>
-      <c r="T20">
+      <c r="T30">
         <v>2.11444091796875</v>
       </c>
-      <c r="U20">
+      <c r="U30">
         <v>1.37030029296875</v>
       </c>
-      <c r="V20">
+      <c r="V30">
         <v>5.6041259765625</v>
       </c>
     </row>
-    <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="1">
+    <row r="31" ht="19.5" customHeight="1">
+      <c r="A31" s="2">
         <v>46223</v>
       </c>
-      <c r="B21">
+      <c r="B31">
         <v>-4.095947265625</v>
       </c>
-      <c r="C21">
+      <c r="C31">
         <v>-2.916748046875</v>
       </c>
-      <c r="D21">
+      <c r="D31">
         <v>-0.80718994140625</v>
       </c>
-      <c r="E21">
+      <c r="E31">
         <v>747.059997558594</v>
       </c>
-      <c r="F21">
+      <c r="F31">
         <v>748.72998046875</v>
       </c>
-      <c r="G21">
+      <c r="G31">
         <v>741.510314941406</v>
       </c>
-      <c r="H21">
+      <c r="H31">
         <v>742.090026855469</v>
       </c>
-      <c r="I21">
+      <c r="I31">
         <v>746.511840820313</v>
       </c>
-      <c r="J21">
+      <c r="J31">
         <v>741.230407714844</v>
       </c>
-      <c r="K21">
+      <c r="K31">
         <v>50422300</v>
       </c>
-      <c r="L21">
+      <c r="L31">
         <v>-0.04998779296875</v>
       </c>
-      <c r="M21">
+      <c r="M31">
         <v>54.0756072998047</v>
       </c>
-      <c r="N21">
+      <c r="N31">
         <v>31.8932228088379</v>
       </c>
-      <c r="O21" t="s">
+      <c r="O31" t="s">
         <v>23</v>
       </c>
-      <c r="P21">
+      <c r="P31">
         <v>-25.7204761505127</v>
       </c>
-      <c r="Q21">
+      <c r="Q31">
         <v>745.7236328125</v>
       </c>
-      <c r="R21">
+      <c r="R31">
         <v>747.726928710938</v>
       </c>
-      <c r="S21">
+      <c r="S31">
         <v>746.918395996094</v>
       </c>
-      <c r="T21">
+      <c r="T31">
         <v>-2.2181396484375</v>
       </c>
-      <c r="U21">
+      <c r="U31">
         <v>-0.2799072265625</v>
       </c>
-      <c r="V21">
+      <c r="V31">
         <v>5.28143310546875</v>
       </c>
     </row>
-    <row r="22" ht="19.5" customHeight="1">
-      <c r="A22" s="1">
+    <row r="32" ht="19.5" customHeight="1">
+      <c r="A32" s="2">
         <v>46220</v>
       </c>
-      <c r="B22">
+      <c r="B32">
         <v>-3.1658935546875</v>
       </c>
-      <c r="C22">
+      <c r="C32">
         <v>-1.37896728515625</v>
       </c>
-      <c r="D22">
+      <c r="D32">
         <v>1.868408203125</v>
       </c>
-      <c r="E22">
+      <c r="E32">
         <v>742.080017089844</v>
       </c>
-      <c r="F22">
+      <c r="F32">
         <v>747.289978027344</v>
       </c>
-      <c r="G22">
+      <c r="G32">
         <v>740.799987792969</v>
       </c>
-      <c r="H22">
+      <c r="H32">
         <v>743.289978027344</v>
       </c>
-      <c r="I22">
+      <c r="I32">
         <v>747.094543457031</v>
       </c>
-      <c r="J22">
+      <c r="J32">
         <v>742.155456542969</v>
       </c>
-      <c r="K22">
+      <c r="K32">
         <v>62650900</v>
       </c>
-      <c r="L22">
+      <c r="L32">
         <v>-0.305225193500519</v>
       </c>
-      <c r="M22">
+      <c r="M32">
         <v>40.9995346069336</v>
       </c>
-      <c r="N22">
+      <c r="N32">
         <v>9.66153240203857</v>
-      </c>
-      <c r="O22" t="s">
-        <v>23</v>
-      </c>
-      <c r="P22">
-        <v>-67.4796676635742</v>
-      </c>
-      <c r="Q22">
-        <v>748.162475585938</v>
-      </c>
-      <c r="R22">
-        <v>749.223571777344</v>
-      </c>
-      <c r="S22">
-        <v>747.397766113281</v>
-      </c>
-      <c r="T22">
-        <v>-0.1954345703125</v>
-      </c>
-      <c r="U22">
-        <v>1.35546875</v>
-      </c>
-      <c r="V22">
-        <v>4.9390869140625</v>
-      </c>
-    </row>
-    <row r="23" ht="19.5" customHeight="1">
-      <c r="A23" s="1">
-        <v>46219</v>
-      </c>
-      <c r="B23">
-        <v>-0.26031494140625</v>
-      </c>
-      <c r="C23">
-        <v>1.78643798828125</v>
-      </c>
-      <c r="D23">
-        <v>4.63775634765625</v>
-      </c>
-      <c r="E23">
-        <v>752.760009765625</v>
-      </c>
-      <c r="F23">
-        <v>754.570007324219</v>
-      </c>
-      <c r="G23">
-        <v>747.880004882813</v>
-      </c>
-      <c r="H23">
-        <v>750.719970703125</v>
-      </c>
-      <c r="I23">
-        <v>753.7822265625</v>
-      </c>
-      <c r="J23">
-        <v>749.197692871094</v>
-      </c>
-      <c r="K23">
-        <v>46409800</v>
-      </c>
-      <c r="L23">
-        <v>-0.563793361186981</v>
-      </c>
-      <c r="M23">
-        <v>37.3873443603516</v>
-      </c>
-      <c r="N23">
-        <v>0.712581157684326</v>
-      </c>
-      <c r="O23" t="s">
-        <v>23</v>
-      </c>
-      <c r="P23">
-        <v>-8.35960674285889</v>
-      </c>
-      <c r="Q23">
-        <v>752.146545410156</v>
-      </c>
-      <c r="R23">
-        <v>750.742126464844</v>
-      </c>
-      <c r="S23">
-        <v>747.801818847656</v>
-      </c>
-      <c r="T23">
-        <v>-0.78778076171875</v>
-      </c>
-      <c r="U23">
-        <v>1.31768798828125</v>
-      </c>
-      <c r="V23">
-        <v>4.58453369140625</v>
-      </c>
-    </row>
-    <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="1">
-        <v>46218</v>
-      </c>
-      <c r="B24">
-        <v>1.14794921875</v>
-      </c>
-      <c r="C24">
-        <v>2.6583251953125</v>
-      </c>
-      <c r="D24">
-        <v>5.79827880859375</v>
-      </c>
-      <c r="E24">
-        <v>754.239990234375</v>
-      </c>
-      <c r="F24">
-        <v>755.580017089844</v>
-      </c>
-      <c r="G24">
-        <v>750.200012207031</v>
-      </c>
-      <c r="H24">
-        <v>754.809997558594</v>
-      </c>
-      <c r="I24">
-        <v>756.966674804688</v>
-      </c>
-      <c r="J24">
-        <v>752.164794921875</v>
-      </c>
-      <c r="K24">
-        <v>43844700</v>
-      </c>
-      <c r="L24">
-        <v>-0.324741899967194</v>
-      </c>
-      <c r="M24">
-        <v>37.1228141784668</v>
-      </c>
-      <c r="N24">
-        <v>-13.9173965454102</v>
-      </c>
-      <c r="O24" t="s">
-        <v>1</v>
-      </c>
-      <c r="P24">
-        <v>28.2575702667236</v>
-      </c>
-      <c r="Q24">
-        <v>753.061279296875</v>
-      </c>
-      <c r="R24">
-        <v>750.523803710938</v>
-      </c>
-      <c r="S24">
-        <v>747.393127441406</v>
-      </c>
-      <c r="T24">
-        <v>1.38665771484375</v>
-      </c>
-      <c r="U24">
-        <v>1.96478271484375</v>
-      </c>
-      <c r="V24">
-        <v>4.8018798828125</v>
-      </c>
-    </row>
-    <row r="25" ht="19.5" customHeight="1">
-      <c r="A25" s="1">
-        <v>46217</v>
-      </c>
-      <c r="B25">
-        <v>1.01629638671875</v>
-      </c>
-      <c r="C25">
-        <v>2.25469970703125</v>
-      </c>
-      <c r="D25">
-        <v>6.17864990234375</v>
-      </c>
-      <c r="E25">
-        <v>750.909973144531</v>
-      </c>
-      <c r="F25">
-        <v>753.340026855469</v>
-      </c>
-      <c r="G25">
-        <v>748.659973144531</v>
-      </c>
-      <c r="H25">
-        <v>751.830017089844</v>
-      </c>
-      <c r="I25">
-        <v>754.606567382813</v>
-      </c>
-      <c r="J25">
-        <v>749.015441894531</v>
-      </c>
-      <c r="K25">
-        <v>35143100</v>
-      </c>
-      <c r="L25">
-        <v>-0.302362352609634</v>
-      </c>
-      <c r="M25">
-        <v>43.124641418457</v>
-      </c>
-      <c r="N25">
-        <v>-6.99629783630371</v>
-      </c>
-      <c r="O25" t="s">
-        <v>23</v>
-      </c>
-      <c r="P25">
-        <v>-0.861863672733307</v>
-      </c>
-      <c r="Q25">
-        <v>751.469848632813</v>
-      </c>
-      <c r="R25">
-        <v>749.436401367188</v>
-      </c>
-      <c r="S25">
-        <v>746.593078613281</v>
-      </c>
-      <c r="T25">
-        <v>1.26654052734375</v>
-      </c>
-      <c r="U25">
-        <v>0.35546875</v>
-      </c>
-      <c r="V25">
-        <v>5.59112548828125</v>
-      </c>
-    </row>
-    <row r="26" ht="19.5" customHeight="1">
-      <c r="A26" s="1">
-        <v>46216</v>
-      </c>
-      <c r="B26">
-        <v>1.46295166015625</v>
-      </c>
-      <c r="C26">
-        <v>3.18304443359375</v>
-      </c>
-      <c r="D26">
-        <v>6.32183837890625</v>
-      </c>
-      <c r="E26">
-        <v>752.469970703125</v>
-      </c>
-      <c r="F26">
-        <v>753.910522460938</v>
-      </c>
-      <c r="G26">
-        <v>748</v>
-      </c>
-      <c r="H26">
-        <v>749.169982910156</v>
-      </c>
-      <c r="I26">
-        <v>752.969604492188</v>
-      </c>
-      <c r="J26">
-        <v>748.6103515625</v>
-      </c>
-      <c r="K26">
-        <v>44013600</v>
-      </c>
-      <c r="L26">
-        <v>0.0823974609375</v>
-      </c>
-      <c r="M26">
-        <v>46.3687362670898</v>
-      </c>
-      <c r="N26">
-        <v>5.96095943450928</v>
-      </c>
-      <c r="O26" t="s">
-        <v>23</v>
-      </c>
-      <c r="P26">
-        <v>-9.41433620452881</v>
-      </c>
-      <c r="Q26">
-        <v>751.109008789063</v>
-      </c>
-      <c r="R26">
-        <v>748.895568847656</v>
-      </c>
-      <c r="S26">
-        <v>746.021179199219</v>
-      </c>
-      <c r="T26">
-        <v>-0.94091796875</v>
-      </c>
-      <c r="U26">
-        <v>0.6103515625</v>
-      </c>
-      <c r="V26">
-        <v>4.3592529296875</v>
-      </c>
-    </row>
-    <row r="27" ht="19.5" customHeight="1">
-      <c r="A27" s="1">
-        <v>46213</v>
-      </c>
-      <c r="B27">
-        <v>3.04345703125</v>
-      </c>
-      <c r="C27">
-        <v>5.25360107421875</v>
-      </c>
-      <c r="D27">
-        <v>6.025634765625</v>
-      </c>
-      <c r="E27">
-        <v>752.049987792969</v>
-      </c>
-      <c r="F27">
-        <v>755.419982910156</v>
-      </c>
-      <c r="G27">
-        <v>748.099975585938</v>
-      </c>
-      <c r="H27">
-        <v>754.950012207031</v>
-      </c>
-      <c r="I27">
-        <v>757.397521972656</v>
-      </c>
-      <c r="J27">
-        <v>752.651977539063</v>
-      </c>
-      <c r="K27">
-        <v>42191300</v>
-      </c>
-      <c r="L27">
-        <v>-0.139508932828903</v>
-      </c>
-      <c r="M27">
-        <v>43.7602081298828</v>
-      </c>
-      <c r="N27">
-        <v>-11.9081888198853</v>
-      </c>
-      <c r="O27" t="s">
-        <v>1</v>
-      </c>
-      <c r="P27">
-        <v>29.8244934082031</v>
-      </c>
-      <c r="Q27">
-        <v>751.974365234375</v>
-      </c>
-      <c r="R27">
-        <v>748.323608398438</v>
-      </c>
-      <c r="S27">
-        <v>745.459045410156</v>
-      </c>
-      <c r="T27">
-        <v>1.9775390625</v>
-      </c>
-      <c r="U27">
-        <v>4.552001953125</v>
-      </c>
-      <c r="V27">
-        <v>4.74554443359375</v>
-      </c>
-    </row>
-    <row r="28" ht="19.5" customHeight="1">
-      <c r="A28" s="1">
-        <v>46212</v>
-      </c>
-      <c r="B28">
-        <v>1.58233642578125</v>
-      </c>
-      <c r="C28">
-        <v>4.81201171875</v>
-      </c>
-      <c r="D28">
-        <v>4.81494140625</v>
-      </c>
-      <c r="E28">
-        <v>747.349975585938</v>
-      </c>
-      <c r="F28">
-        <v>751.969970703125</v>
-      </c>
-      <c r="G28">
-        <v>745.590026855469</v>
-      </c>
-      <c r="H28">
-        <v>751.710021972656</v>
-      </c>
-      <c r="I28">
-        <v>754.285522460938</v>
-      </c>
-      <c r="J28">
-        <v>748.920166015625</v>
-      </c>
-      <c r="K28">
-        <v>41441700</v>
-      </c>
-      <c r="L28">
-        <v>-0.590939462184906</v>
-      </c>
-      <c r="M28">
-        <v>49.6756820678711</v>
-      </c>
-      <c r="N28">
-        <v>-9.37797546386719</v>
-      </c>
-      <c r="O28" t="s">
-        <v>1</v>
-      </c>
-      <c r="P28">
-        <v>18.6884059906006</v>
-      </c>
-      <c r="Q28">
-        <v>748.9482421875</v>
-      </c>
-      <c r="R28">
-        <v>746.446655273438</v>
-      </c>
-      <c r="S28">
-        <v>744.349548339844</v>
-      </c>
-      <c r="T28">
-        <v>2.3155517578125</v>
-      </c>
-      <c r="U28">
-        <v>3.33013916015625</v>
-      </c>
-      <c r="V28">
-        <v>5.3653564453125</v>
-      </c>
-    </row>
-    <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="1">
-        <v>46211</v>
-      </c>
-      <c r="B29">
-        <v>-0.99468994140625</v>
-      </c>
-      <c r="C29">
-        <v>4.4906005859375</v>
-      </c>
-      <c r="D29">
-        <v>3.17181396484375</v>
-      </c>
-      <c r="E29">
-        <v>743.159973144531</v>
-      </c>
-      <c r="F29">
-        <v>746.150024414063</v>
-      </c>
-      <c r="G29">
-        <v>739.510009765625</v>
-      </c>
-      <c r="H29">
-        <v>745.400024414063</v>
-      </c>
-      <c r="I29">
-        <v>747.537963867188</v>
-      </c>
-      <c r="J29">
-        <v>741.815368652344</v>
-      </c>
-      <c r="K29">
-        <v>43767300</v>
-      </c>
-      <c r="L29">
-        <v>-0.995704293251038</v>
-      </c>
-      <c r="M29">
-        <v>54.8163452148438</v>
-      </c>
-      <c r="N29">
-        <v>-17.3321285247803</v>
-      </c>
-      <c r="O29" t="s">
-        <v>23</v>
-      </c>
-      <c r="P29">
-        <v>-29.858362197876</v>
-      </c>
-      <c r="Q29">
-        <v>746.258422851563</v>
-      </c>
-      <c r="R29">
-        <v>744.976745605469</v>
-      </c>
-      <c r="S29">
-        <v>743.473571777344</v>
-      </c>
-      <c r="T29">
-        <v>1.387939453125</v>
-      </c>
-      <c r="U29">
-        <v>2.30535888671875</v>
-      </c>
-      <c r="V29">
-        <v>5.72259521484375</v>
-      </c>
-    </row>
-    <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="1">
-        <v>46210</v>
-      </c>
-      <c r="B30">
-        <v>0.88140869140625</v>
-      </c>
-      <c r="C30">
-        <v>6.25091552734375</v>
-      </c>
-      <c r="D30">
-        <v>2.718505859375</v>
-      </c>
-      <c r="E30">
-        <v>750.219970703125</v>
-      </c>
-      <c r="F30">
-        <v>750.960021972656</v>
-      </c>
-      <c r="G30">
-        <v>745.210021972656</v>
-      </c>
-      <c r="H30">
-        <v>747.710021972656</v>
-      </c>
-      <c r="I30">
-        <v>750.022277832031</v>
-      </c>
-      <c r="J30">
-        <v>745.5947265625</v>
-      </c>
-      <c r="K30">
-        <v>43721400</v>
-      </c>
-      <c r="L30">
-        <v>-1.80523097515106</v>
-      </c>
-      <c r="M30">
-        <v>66.3091278076172</v>
-      </c>
-      <c r="N30">
-        <v>-2.38608145713806</v>
-      </c>
-      <c r="O30" t="s">
-        <v>23</v>
-      </c>
-      <c r="P30">
-        <v>-6.23193979263306</v>
-      </c>
-      <c r="Q30">
-        <v>747.609436035156</v>
-      </c>
-      <c r="R30">
-        <v>744.811157226563</v>
-      </c>
-      <c r="S30">
-        <v>743.291320800781</v>
-      </c>
-      <c r="T30">
-        <v>-0.937744140625</v>
-      </c>
-      <c r="U30">
-        <v>0.38470458984375</v>
-      </c>
-      <c r="V30">
-        <v>4.42755126953125</v>
-      </c>
-    </row>
-    <row r="31" ht="19.5" customHeight="1">
-      <c r="A31" s="1">
-        <v>46209</v>
-      </c>
-      <c r="B31">
-        <v>2.95452880859375</v>
-      </c>
-      <c r="C31">
-        <v>5.9378662109375</v>
-      </c>
-      <c r="D31">
-        <v>2.21661376953125</v>
-      </c>
-      <c r="E31">
-        <v>748.739990234375</v>
-      </c>
-      <c r="F31">
-        <v>752.409973144531</v>
-      </c>
-      <c r="G31">
-        <v>747.409973144531</v>
-      </c>
-      <c r="H31">
-        <v>751.280029296875</v>
-      </c>
-      <c r="I31">
-        <v>754.38818359375</v>
-      </c>
-      <c r="J31">
-        <v>748.0263671875</v>
-      </c>
-      <c r="K31">
-        <v>50673300</v>
-      </c>
-      <c r="L31">
-        <v>-1.4480881690979</v>
-      </c>
-      <c r="M31">
-        <v>67.9299926757813</v>
-      </c>
-      <c r="N31">
-        <v>1.67483258247375</v>
-      </c>
-      <c r="O31" t="s">
-        <v>1</v>
-      </c>
-      <c r="P31">
-        <v>31.4023609161377</v>
-      </c>
-      <c r="Q31">
-        <v>747.444946289063</v>
-      </c>
-      <c r="R31">
-        <v>743.92333984375</v>
-      </c>
-      <c r="S31">
-        <v>742.758056640625</v>
-      </c>
-      <c r="T31">
-        <v>1.97821044921875</v>
-      </c>
-      <c r="U31">
-        <v>0.61639404296875</v>
-      </c>
-      <c r="V31">
-        <v>6.36181640625</v>
-      </c>
-    </row>
-    <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" s="1">
-        <v>46205</v>
-      </c>
-      <c r="B32">
-        <v>2.69488525390625</v>
-      </c>
-      <c r="C32">
-        <v>3.70648193359375</v>
-      </c>
-      <c r="D32">
-        <v>0.73291015625</v>
-      </c>
-      <c r="E32">
-        <v>747.400024414063</v>
-      </c>
-      <c r="F32">
-        <v>751.309997558594</v>
-      </c>
-      <c r="G32">
-        <v>740.030029296875</v>
-      </c>
-      <c r="H32">
-        <v>744.780029296875</v>
-      </c>
-      <c r="I32">
-        <v>747.477478027344</v>
-      </c>
-      <c r="J32">
-        <v>739.211059570313</v>
-      </c>
-      <c r="K32">
-        <v>57505900</v>
-      </c>
-      <c r="L32">
-        <v>-1.75523447990417</v>
-      </c>
-      <c r="M32">
-        <v>66.8110198974609</v>
-      </c>
-      <c r="N32">
-        <v>4.79237604141235</v>
       </c>
       <c r="O32" t="s">
         <v>23</v>
       </c>
       <c r="P32">
-        <v>-9.36024951934814</v>
+        <v>-67.4796676635742</v>
       </c>
       <c r="Q32">
-        <v>743.651916503906</v>
+        <v>748.162475585938</v>
       </c>
       <c r="R32">
-        <v>742.069030761719</v>
+        <v>749.223571777344</v>
       </c>
       <c r="S32">
-        <v>741.8056640625</v>
+        <v>747.397766113281</v>
       </c>
       <c r="T32">
-        <v>-3.83251953125</v>
+        <v>-0.1954345703125</v>
       </c>
       <c r="U32">
-        <v>-0.8189697265625</v>
+        <v>1.35546875</v>
       </c>
       <c r="V32">
-        <v>8.26641845703125</v>
+        <v>4.9390869140625</v>
       </c>
     </row>
     <row r="33" ht="19.5" customHeight="1">
-      <c r="A33" s="1">
-        <v>46204</v>
+      <c r="A33" s="2">
+        <v>46219</v>
       </c>
       <c r="B33">
-        <v>5.459716796875</v>
+        <v>-0.26031494140625</v>
       </c>
       <c r="C33">
-        <v>3.53753662109375</v>
+        <v>1.78643798828125</v>
       </c>
       <c r="D33">
-        <v>1.20068359375</v>
+        <v>4.63775634765625</v>
       </c>
       <c r="E33">
-        <v>745</v>
+        <v>752.760009765625</v>
       </c>
       <c r="F33">
-        <v>749.434997558594</v>
+        <v>754.570007324219</v>
       </c>
       <c r="G33">
-        <v>742.375</v>
+        <v>747.880004882813</v>
       </c>
       <c r="H33">
-        <v>745.760009765625</v>
+        <v>750.719970703125</v>
       </c>
       <c r="I33">
-        <v>747.958740234375</v>
+        <v>753.7822265625</v>
       </c>
       <c r="J33">
-        <v>742.375549316406</v>
+        <v>749.197692871094</v>
       </c>
       <c r="K33">
-        <v>47100800</v>
+        <v>46409800</v>
       </c>
       <c r="L33">
-        <v>-1.509521484375</v>
+        <v>-0.563793361186981</v>
       </c>
       <c r="M33">
-        <v>63.7556114196777</v>
+        <v>37.3873443603516</v>
       </c>
       <c r="N33">
-        <v>13.156925201416</v>
+        <v>0.712581157684326</v>
       </c>
       <c r="O33" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P33">
-        <v>7.21037817001343</v>
+        <v>-8.35960674285889</v>
       </c>
       <c r="Q33">
-        <v>743.49072265625</v>
+        <v>752.146545410156</v>
       </c>
       <c r="R33">
-        <v>741.38427734375</v>
+        <v>750.742126464844</v>
       </c>
       <c r="S33">
-        <v>741.459350585938</v>
+        <v>747.801818847656</v>
       </c>
       <c r="T33">
-        <v>-1.47625732421875</v>
+        <v>-0.78778076171875</v>
       </c>
       <c r="U33">
-        <v>0.00054931640625</v>
+        <v>1.31768798828125</v>
       </c>
       <c r="V33">
-        <v>5.58319091796875</v>
+        <v>4.58453369140625</v>
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1">
-      <c r="A34" s="1">
-        <v>46203</v>
+      <c r="A34" s="2">
+        <v>46218</v>
       </c>
       <c r="B34">
-        <v>6.88262939453125</v>
+        <v>1.14794921875</v>
       </c>
       <c r="C34">
-        <v>0.70989990234375</v>
+        <v>2.6583251953125</v>
       </c>
       <c r="D34">
-        <v>0.00537109375</v>
+        <v>5.79827880859375</v>
       </c>
       <c r="E34">
-        <v>741.289978027344</v>
+        <v>754.239990234375</v>
       </c>
       <c r="F34">
-        <v>748.02001953125</v>
+        <v>755.580017089844</v>
       </c>
       <c r="G34">
-        <v>740.890014648438</v>
+        <v>750.200012207031</v>
       </c>
       <c r="H34">
-        <v>746.77001953125</v>
+        <v>754.809997558594</v>
       </c>
       <c r="I34">
-        <v>749.591796875</v>
+        <v>756.966674804688</v>
       </c>
       <c r="J34">
-        <v>744.273864746094</v>
+        <v>752.164794921875</v>
       </c>
       <c r="K34">
-        <v>55626000</v>
+        <v>43844700</v>
       </c>
       <c r="L34">
-        <v>-1.39428424835205</v>
+        <v>-0.324741899967194</v>
       </c>
       <c r="M34">
-        <v>56.3426513671875</v>
+        <v>37.1228141784668</v>
       </c>
       <c r="N34">
-        <v>-15.8709001541138</v>
+        <v>-13.9173965454102</v>
       </c>
       <c r="O34" t="s">
         <v>1</v>
       </c>
       <c r="P34">
-        <v>52.5797996520996</v>
+        <v>28.2575702667236</v>
       </c>
       <c r="Q34">
-        <v>741.621215820313</v>
+        <v>753.061279296875</v>
       </c>
       <c r="R34">
-        <v>739.870544433594</v>
+        <v>750.523803710938</v>
       </c>
       <c r="S34">
-        <v>740.920654296875</v>
+        <v>747.393127441406</v>
       </c>
       <c r="T34">
-        <v>1.57177734375</v>
+        <v>1.38665771484375</v>
       </c>
       <c r="U34">
-        <v>3.38385009765625</v>
+        <v>1.96478271484375</v>
       </c>
       <c r="V34">
-        <v>5.31793212890625</v>
+        <v>4.8018798828125</v>
       </c>
     </row>
     <row r="35" ht="19.5" customHeight="1">
-      <c r="A35" s="1">
-        <v>46202</v>
+      <c r="A35" s="2">
+        <v>46217</v>
       </c>
       <c r="B35">
-        <v>3.24554443359375</v>
+        <v>1.01629638671875</v>
       </c>
       <c r="C35">
-        <v>-4.11358642578125</v>
+        <v>2.25469970703125</v>
       </c>
       <c r="D35">
-        <v>-2.13055419921875</v>
+        <v>6.17864990234375</v>
       </c>
       <c r="E35">
-        <v>736.530029296875</v>
+        <v>750.909973144531</v>
       </c>
       <c r="F35">
-        <v>741.559997558594</v>
+        <v>753.340026855469</v>
       </c>
       <c r="G35">
-        <v>732.090026855469</v>
+        <v>748.659973144531</v>
       </c>
       <c r="H35">
-        <v>741</v>
+        <v>751.830017089844</v>
       </c>
       <c r="I35">
-        <v>746.138854980469</v>
+        <v>754.606567382813</v>
       </c>
       <c r="J35">
-        <v>736.758056640625</v>
+        <v>749.015441894531</v>
       </c>
       <c r="K35">
-        <v>58035200</v>
+        <v>35143100</v>
       </c>
       <c r="L35">
-        <v>-1.6276216506958</v>
+        <v>-0.302362352609634</v>
       </c>
       <c r="M35">
-        <v>66.9716567993164</v>
+        <v>43.124641418457</v>
       </c>
       <c r="N35">
-        <v>-9.74757289886475</v>
+        <v>-6.99629783630371</v>
       </c>
       <c r="O35" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P35">
-        <v>62.1432952880859</v>
+        <v>-0.861863672733307</v>
       </c>
       <c r="Q35">
-        <v>736.351501464844</v>
+        <v>751.469848632813</v>
       </c>
       <c r="R35">
-        <v>737.890869140625</v>
+        <v>749.436401367188</v>
       </c>
       <c r="S35">
-        <v>740.243469238281</v>
+        <v>746.593078613281</v>
       </c>
       <c r="T35">
-        <v>4.578857421875</v>
+        <v>1.26654052734375</v>
       </c>
       <c r="U35">
-        <v>4.66802978515625</v>
+        <v>0.35546875</v>
       </c>
       <c r="V35">
-        <v>9.38079833984375</v>
+        <v>5.59112548828125</v>
       </c>
     </row>
     <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="1">
-        <v>46199</v>
+      <c r="A36" s="2">
+        <v>46216</v>
       </c>
       <c r="B36">
-        <v>-5.0906982421875</v>
+        <v>1.46295166015625</v>
       </c>
       <c r="C36">
-        <v>-7.74395751953125</v>
+        <v>3.18304443359375</v>
       </c>
       <c r="D36">
-        <v>-3.71441650390625</v>
+        <v>6.32183837890625</v>
       </c>
       <c r="E36">
-        <v>728.950012207031</v>
+        <v>752.469970703125</v>
       </c>
       <c r="F36">
-        <v>736.530029296875</v>
+        <v>753.910522460938</v>
       </c>
       <c r="G36">
-        <v>716.580017089844</v>
+        <v>748</v>
       </c>
       <c r="H36">
-        <v>728.989990234375</v>
+        <v>749.169982910156</v>
       </c>
       <c r="I36">
-        <v>732.542541503906</v>
+        <v>752.969604492188</v>
       </c>
       <c r="J36">
-        <v>721.128601074219</v>
+        <v>748.6103515625</v>
       </c>
       <c r="K36">
-        <v>71033904</v>
+        <v>44013600</v>
       </c>
       <c r="L36">
-        <v>-1.63333570957184</v>
+        <v>0.0823974609375</v>
       </c>
       <c r="M36">
-        <v>74.2048263549805</v>
+        <v>46.3687362670898</v>
       </c>
       <c r="N36">
-        <v>-6.28943967819214</v>
+        <v>5.96095943450928</v>
       </c>
       <c r="O36" t="s">
         <v>23</v>
       </c>
       <c r="P36">
-        <v>-30.6265525817871</v>
+        <v>-9.41433620452881</v>
       </c>
       <c r="Q36">
-        <v>731.398254394531</v>
+        <v>751.109008789063</v>
       </c>
       <c r="R36">
-        <v>736.694763183594</v>
+        <v>748.895568847656</v>
       </c>
       <c r="S36">
-        <v>740.088500976563</v>
+        <v>746.021179199219</v>
       </c>
       <c r="T36">
-        <v>-3.98748779296875</v>
+        <v>-0.94091796875</v>
       </c>
       <c r="U36">
-        <v>4.548583984375</v>
+        <v>0.6103515625</v>
       </c>
       <c r="V36">
-        <v>11.4139404296875</v>
+        <v>4.3592529296875</v>
       </c>
     </row>
     <row r="37" ht="19.5" customHeight="1">
-      <c r="A37" s="1">
-        <v>46198</v>
+      <c r="A37" s="2">
+        <v>46213</v>
       </c>
       <c r="B37">
-        <v>-4.12738037109375</v>
+        <v>3.04345703125</v>
       </c>
       <c r="C37">
-        <v>-5.62493896484375</v>
+        <v>5.25360107421875</v>
       </c>
       <c r="D37">
-        <v>-2.584716796875</v>
+        <v>6.025634765625</v>
       </c>
       <c r="E37">
-        <v>738.909973144531</v>
+        <v>752.049987792969</v>
       </c>
       <c r="F37">
-        <v>739.369995117188</v>
+        <v>755.419982910156</v>
       </c>
       <c r="G37">
-        <v>729.599975585938</v>
+        <v>748.099975585938</v>
       </c>
       <c r="H37">
-        <v>734.299987792969</v>
+        <v>754.950012207031</v>
       </c>
       <c r="I37">
-        <v>738.064086914063</v>
+        <v>757.397521972656</v>
       </c>
       <c r="J37">
-        <v>729.988830566406</v>
+        <v>752.651977539063</v>
       </c>
       <c r="K37">
-        <v>54128000</v>
+        <v>42191300</v>
       </c>
       <c r="L37">
-        <v>-1.65523850917816</v>
+        <v>-0.139508932828903</v>
       </c>
       <c r="M37">
-        <v>79.1851272583008</v>
+        <v>43.7602081298828</v>
       </c>
       <c r="N37">
-        <v>-6.69492769241333</v>
+        <v>-11.9081888198853</v>
       </c>
       <c r="O37" t="s">
         <v>1</v>
       </c>
       <c r="P37">
-        <v>12.2647380828857</v>
+        <v>29.8244934082031</v>
       </c>
       <c r="Q37">
-        <v>735.235107421875</v>
+        <v>751.974365234375</v>
       </c>
       <c r="R37">
-        <v>738.96923828125</v>
+        <v>748.323608398438</v>
       </c>
       <c r="S37">
-        <v>741.535400390625</v>
+        <v>745.459045410156</v>
       </c>
       <c r="T37">
-        <v>-1.305908203125</v>
+        <v>1.9775390625</v>
       </c>
       <c r="U37">
-        <v>0.38885498046875</v>
+        <v>4.552001953125</v>
       </c>
       <c r="V37">
-        <v>8.07525634765625</v>
+        <v>4.74554443359375</v>
       </c>
     </row>
     <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="1">
-        <v>46197</v>
+      <c r="A38" s="2">
+        <v>46212</v>
       </c>
       <c r="B38">
-        <v>-5.0550537109375</v>
+        <v>1.58233642578125</v>
       </c>
       <c r="C38">
-        <v>-2.88189697265625</v>
+        <v>4.81201171875</v>
       </c>
       <c r="D38">
-        <v>-2.1800537109375</v>
+        <v>4.81494140625</v>
       </c>
       <c r="E38">
-        <v>735.169982910156</v>
+        <v>747.349975585938</v>
       </c>
       <c r="F38">
-        <v>739.945007324219</v>
+        <v>751.969970703125</v>
       </c>
       <c r="G38">
-        <v>730.840026855469</v>
+        <v>745.590026855469</v>
       </c>
       <c r="H38">
-        <v>733.239990234375</v>
+        <v>751.710021972656</v>
       </c>
       <c r="I38">
-        <v>737.097229003906</v>
+        <v>754.285522460938</v>
       </c>
       <c r="J38">
-        <v>729.545532226563</v>
+        <v>748.920166015625</v>
       </c>
       <c r="K38">
-        <v>57439500</v>
+        <v>41441700</v>
       </c>
       <c r="L38">
-        <v>-1.40809559822083</v>
+        <v>-0.590939462184906</v>
       </c>
       <c r="M38">
-        <v>84.8669052124023</v>
+        <v>49.6756820678711</v>
       </c>
       <c r="N38">
-        <v>5.94319248199463</v>
+        <v>-9.37797546386719</v>
       </c>
       <c r="O38" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P38">
-        <v>-9.52979946136475</v>
+        <v>18.6884059906006</v>
       </c>
       <c r="Q38">
-        <v>736.359680175781</v>
+        <v>748.9482421875</v>
       </c>
       <c r="R38">
-        <v>740.5546875</v>
+        <v>746.446655273438</v>
       </c>
       <c r="S38">
-        <v>742.377014160156</v>
+        <v>744.349548339844</v>
       </c>
       <c r="T38">
-        <v>-2.8477783203125</v>
+        <v>2.3155517578125</v>
       </c>
       <c r="U38">
-        <v>-1.29449462890625</v>
+        <v>3.33013916015625</v>
       </c>
       <c r="V38">
-        <v>7.55169677734375</v>
+        <v>5.3653564453125</v>
       </c>
     </row>
     <row r="39" ht="19.5" customHeight="1">
-      <c r="A39" s="1">
-        <v>46196</v>
+      <c r="A39" s="2">
+        <v>46211</v>
       </c>
       <c r="B39">
-        <v>-5.61041259765625</v>
+        <v>-0.99468994140625</v>
       </c>
       <c r="C39">
-        <v>-0.48480224609375</v>
+        <v>4.4906005859375</v>
       </c>
       <c r="D39">
-        <v>-1.7640380859375</v>
+        <v>3.17181396484375</v>
       </c>
       <c r="E39">
-        <v>733.809997558594</v>
+        <v>743.159973144531</v>
       </c>
       <c r="F39">
-        <v>739.630004882813</v>
+        <v>746.150024414063</v>
       </c>
       <c r="G39">
-        <v>732.299987792969</v>
+        <v>739.510009765625</v>
       </c>
       <c r="H39">
-        <v>733.580017089844</v>
+        <v>745.400024414063</v>
       </c>
       <c r="I39">
-        <v>737.086975097656</v>
+        <v>747.537963867188</v>
       </c>
       <c r="J39">
-        <v>731.193054199219</v>
+        <v>741.815368652344</v>
       </c>
       <c r="K39">
-        <v>66846700</v>
+        <v>43767300</v>
       </c>
       <c r="L39">
-        <v>-1.34476149082184</v>
+        <v>-0.995704293251038</v>
       </c>
       <c r="M39">
-        <v>80.1060485839844</v>
+        <v>54.8163452148438</v>
       </c>
       <c r="N39">
-        <v>-4.6582145690918</v>
+        <v>-17.3321285247803</v>
       </c>
       <c r="O39" t="s">
         <v>23</v>
       </c>
       <c r="P39">
-        <v>-48.3262519836426</v>
+        <v>-29.858362197876</v>
       </c>
       <c r="Q39">
-        <v>739.430358886719</v>
+        <v>746.258422851563</v>
       </c>
       <c r="R39">
-        <v>742.441955566406</v>
+        <v>744.976745605469</v>
       </c>
       <c r="S39">
-        <v>743.275939941406</v>
+        <v>743.473571777344</v>
       </c>
       <c r="T39">
-        <v>-2.54302978515625</v>
+        <v>1.387939453125</v>
       </c>
       <c r="U39">
-        <v>-1.10693359375</v>
+        <v>2.30535888671875</v>
       </c>
       <c r="V39">
-        <v>5.8939208984375</v>
+        <v>5.72259521484375</v>
       </c>
     </row>
     <row r="40" ht="19.5" customHeight="1">
-      <c r="A40" s="1">
-        <v>46195</v>
+      <c r="A40" s="2">
+        <v>46210</v>
       </c>
       <c r="B40">
-        <v>-2.591552734375</v>
+        <v>0.88140869140625</v>
       </c>
       <c r="C40">
-        <v>2.92681884765625</v>
+        <v>6.25091552734375</v>
       </c>
       <c r="D40">
-        <v>-0.6483154296875</v>
+        <v>2.718505859375</v>
       </c>
       <c r="E40">
-        <v>747.700012207031</v>
+        <v>750.219970703125</v>
       </c>
       <c r="F40">
-        <v>750.179992675781</v>
+        <v>750.960021972656</v>
       </c>
       <c r="G40">
-        <v>743.130004882813</v>
+        <v>745.210021972656</v>
       </c>
       <c r="H40">
-        <v>744.390014648438</v>
+        <v>747.710021972656</v>
       </c>
       <c r="I40">
-        <v>747.045654296875</v>
+        <v>750.022277832031</v>
       </c>
       <c r="J40">
-        <v>742.430358886719</v>
+        <v>745.5947265625</v>
       </c>
       <c r="K40">
-        <v>46628000</v>
+        <v>43721400</v>
       </c>
       <c r="L40">
-        <v>-1.1395263671875</v>
+        <v>-1.80523097515106</v>
       </c>
       <c r="M40">
-        <v>84.0198745727539</v>
+        <v>66.3091278076172</v>
       </c>
       <c r="N40">
-        <v>4.99104022979736</v>
+        <v>-2.38608145713806</v>
       </c>
       <c r="O40" t="s">
         <v>23</v>
       </c>
       <c r="P40">
-        <v>-3.24120903015137</v>
+        <v>-6.23193979263306</v>
       </c>
       <c r="Q40">
-        <v>744.905395507813</v>
+        <v>747.609436035156</v>
       </c>
       <c r="R40">
-        <v>744.58984375</v>
+        <v>744.811157226563</v>
       </c>
       <c r="S40">
-        <v>744.183654785156</v>
+        <v>743.291320800781</v>
       </c>
       <c r="T40">
-        <v>-3.13433837890625</v>
+        <v>-0.937744140625</v>
       </c>
       <c r="U40">
-        <v>-0.69964599609375</v>
+        <v>0.38470458984375</v>
       </c>
       <c r="V40">
-        <v>4.61529541015625</v>
+        <v>4.42755126953125</v>
       </c>
     </row>
     <row r="41" ht="19.5" customHeight="1">
-      <c r="A41" s="1">
-        <v>46191</v>
+      <c r="A41" s="2">
+        <v>46209</v>
       </c>
       <c r="B41">
-        <v>-1.58734130859375</v>
+        <v>2.95452880859375</v>
       </c>
       <c r="C41">
-        <v>3.81500244140625</v>
+        <v>5.9378662109375</v>
       </c>
       <c r="D41">
-        <v>-1.35107421875</v>
+        <v>2.21661376953125</v>
       </c>
       <c r="E41">
-        <v>747.760009765625</v>
+        <v>748.739990234375</v>
       </c>
       <c r="F41">
-        <v>748.22998046875</v>
+        <v>752.409973144531</v>
       </c>
       <c r="G41">
-        <v>743.859985351563</v>
+        <v>747.409973144531</v>
       </c>
       <c r="H41">
-        <v>746.739990234375</v>
+        <v>751.280029296875</v>
       </c>
       <c r="I41">
-        <v>750.319641113281</v>
+        <v>754.38818359375</v>
       </c>
       <c r="J41">
-        <v>742.322143554688</v>
+        <v>748.0263671875</v>
       </c>
       <c r="K41">
-        <v>80875600</v>
+        <v>50673300</v>
       </c>
       <c r="L41">
-        <v>-0.718098938465118</v>
+        <v>-1.4480881690979</v>
       </c>
       <c r="M41">
-        <v>80.0257568359375</v>
+        <v>67.9299926757813</v>
       </c>
       <c r="N41">
-        <v>4.03029108047485</v>
+        <v>1.67483258247375</v>
       </c>
       <c r="O41" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P41">
-        <v>-1.25619208812714</v>
+        <v>31.4023609161377</v>
       </c>
       <c r="Q41">
-        <v>745.206298828125</v>
+        <v>747.444946289063</v>
       </c>
       <c r="R41">
-        <v>744.63818359375</v>
+        <v>743.92333984375</v>
       </c>
       <c r="S41">
-        <v>744.055541992188</v>
+        <v>742.758056640625</v>
       </c>
       <c r="T41">
-        <v>2.08966064453125</v>
+        <v>1.97821044921875</v>
       </c>
       <c r="U41">
-        <v>-1.537841796875</v>
+        <v>0.61639404296875</v>
       </c>
       <c r="V41">
-        <v>7.99749755859375</v>
+        <v>6.36181640625</v>
       </c>
     </row>
     <row r="42" ht="19.5" customHeight="1">
-      <c r="A42" s="1">
-        <v>46190</v>
+      <c r="A42" s="2">
+        <v>46205</v>
       </c>
       <c r="B42">
-        <v>-2.04083251953125</v>
+        <v>2.69488525390625</v>
       </c>
       <c r="C42">
-        <v>2.4857177734375</v>
+        <v>3.70648193359375</v>
       </c>
       <c r="D42">
-        <v>-2.19775390625</v>
+        <v>0.73291015625</v>
       </c>
       <c r="E42">
-        <v>751.289978027344</v>
+        <v>747.400024414063</v>
       </c>
       <c r="F42">
-        <v>752.150024414063</v>
+        <v>751.309997558594</v>
       </c>
       <c r="G42">
-        <v>739.219970703125</v>
+        <v>740.030029296875</v>
       </c>
       <c r="H42">
-        <v>740.960021972656</v>
+        <v>744.780029296875</v>
       </c>
       <c r="I42">
-        <v>743.736389160156</v>
+        <v>747.477478027344</v>
       </c>
       <c r="J42">
-        <v>734.656616210938</v>
+        <v>739.211059570313</v>
       </c>
       <c r="K42">
-        <v>85945200</v>
+        <v>57505900</v>
       </c>
       <c r="L42">
-        <v>-0.719528913497925</v>
+        <v>-1.75523447990417</v>
       </c>
       <c r="M42">
-        <v>76.9254379272461</v>
+        <v>66.8110198974609</v>
       </c>
       <c r="N42">
-        <v>11.3856058120728</v>
+        <v>4.79237604141235</v>
       </c>
       <c r="O42" t="s">
         <v>23</v>
       </c>
       <c r="P42">
-        <v>-58.2087860107422</v>
+        <v>-9.36024951934814</v>
       </c>
       <c r="Q42">
-        <v>743.9501953125</v>
+        <v>743.651916503906</v>
       </c>
       <c r="R42">
-        <v>744.424499511719</v>
+        <v>742.069030761719</v>
       </c>
       <c r="S42">
-        <v>743.818603515625</v>
+        <v>741.8056640625</v>
       </c>
       <c r="T42">
-        <v>-8.41363525390625</v>
+        <v>-3.83251953125</v>
       </c>
       <c r="U42">
-        <v>-4.5633544921875</v>
+        <v>-0.8189697265625</v>
       </c>
       <c r="V42">
-        <v>9.07977294921875</v>
+        <v>8.26641845703125</v>
       </c>
     </row>
     <row r="43" ht="19.5" customHeight="1">
-      <c r="A43" s="1">
-        <v>46189</v>
+      <c r="A43" s="2">
+        <v>46204</v>
       </c>
       <c r="B43">
-        <v>7.6658935546875</v>
+        <v>5.459716796875</v>
       </c>
       <c r="C43">
-        <v>3.96209716796875</v>
+        <v>3.53753662109375</v>
       </c>
       <c r="D43">
-        <v>-1.35247802734375</v>
+        <v>1.20068359375</v>
       </c>
       <c r="E43">
-        <v>754.549987792969</v>
+        <v>745</v>
       </c>
       <c r="F43">
-        <v>755.440002441406</v>
+        <v>749.434997558594</v>
       </c>
       <c r="G43">
-        <v>749.880004882813</v>
+        <v>742.375</v>
       </c>
       <c r="H43">
-        <v>750.330017089844</v>
+        <v>745.760009765625</v>
       </c>
       <c r="I43">
-        <v>751.783935546875</v>
+        <v>747.958740234375</v>
       </c>
       <c r="J43">
-        <v>747.366333007813</v>
+        <v>742.375549316406</v>
       </c>
       <c r="K43">
-        <v>67093100</v>
+        <v>47100800</v>
       </c>
       <c r="L43">
-        <v>-0.283816397190094</v>
+        <v>-1.509521484375</v>
       </c>
       <c r="M43">
-        <v>69.0622787475586</v>
+        <v>63.7556114196777</v>
       </c>
       <c r="N43">
-        <v>12.0432567596436</v>
+        <v>13.156925201416</v>
       </c>
       <c r="O43" t="s">
         <v>1</v>
       </c>
       <c r="P43">
-        <v>8.51707363128662</v>
+        <v>7.21037817001343</v>
       </c>
       <c r="Q43">
-        <v>748.120727539063</v>
+        <v>743.49072265625</v>
       </c>
       <c r="R43">
-        <v>745.5869140625</v>
+        <v>741.38427734375</v>
       </c>
       <c r="S43">
-        <v>744.132934570313</v>
+        <v>741.459350585938</v>
       </c>
       <c r="T43">
-        <v>-3.65606689453125</v>
+        <v>-1.47625732421875</v>
       </c>
       <c r="U43">
-        <v>-2.513671875</v>
+        <v>0.00054931640625</v>
       </c>
       <c r="V43">
-        <v>4.4176025390625</v>
+        <v>5.58319091796875</v>
       </c>
     </row>
     <row r="44" ht="19.5" customHeight="1">
-      <c r="A44" s="1">
-        <v>46188</v>
+      <c r="A44" s="2">
+        <v>46203</v>
       </c>
       <c r="B44">
-        <v>10.0482177734375</v>
+        <v>6.88262939453125</v>
       </c>
       <c r="C44">
-        <v>1.11309814453125</v>
+        <v>0.70989990234375</v>
       </c>
       <c r="D44">
-        <v>-3.2767333984375</v>
+        <v>0.00537109375</v>
       </c>
       <c r="E44">
-        <v>751.849975585938</v>
+        <v>741.289978027344</v>
       </c>
       <c r="F44">
-        <v>756.679992675781</v>
+        <v>748.02001953125</v>
       </c>
       <c r="G44">
-        <v>751.760009765625</v>
+        <v>740.890014648438</v>
       </c>
       <c r="H44">
-        <v>754.830017089844</v>
+        <v>746.77001953125</v>
       </c>
       <c r="I44">
-        <v>756.992736816406</v>
+        <v>749.591796875</v>
       </c>
       <c r="J44">
-        <v>751.517578125</v>
+        <v>744.273864746094</v>
       </c>
       <c r="K44">
-        <v>60176400</v>
+        <v>55626000</v>
       </c>
       <c r="L44">
-        <v>-0.207627072930336</v>
+        <v>-1.39428424835205</v>
       </c>
       <c r="M44">
-        <v>61.6389427185059</v>
+        <v>56.3426513671875</v>
       </c>
       <c r="N44">
-        <v>-5.95076656341553</v>
+        <v>-15.8709001541138</v>
       </c>
       <c r="O44" t="s">
         <v>1</v>
       </c>
       <c r="P44">
-        <v>100</v>
+        <v>52.5797996520996</v>
       </c>
       <c r="Q44">
-        <v>746.413208007813</v>
+        <v>741.621215820313</v>
       </c>
       <c r="R44">
-        <v>744.198059082031</v>
+        <v>739.870544433594</v>
       </c>
       <c r="S44">
-        <v>743.303833007813</v>
+        <v>740.920654296875</v>
       </c>
       <c r="T44">
-        <v>0.312744140625</v>
+        <v>1.57177734375</v>
       </c>
       <c r="U44">
-        <v>-0.242431640625</v>
+        <v>3.38385009765625</v>
       </c>
       <c r="V44">
-        <v>5.47515869140625</v>
+        <v>5.31793212890625</v>
+      </c>
+    </row>
+    <row r="45" ht="19.5" customHeight="1">
+      <c r="A45" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B45">
+        <v>3.24554443359375</v>
+      </c>
+      <c r="C45">
+        <v>-4.11358642578125</v>
+      </c>
+      <c r="D45">
+        <v>-2.13055419921875</v>
+      </c>
+      <c r="E45">
+        <v>736.530029296875</v>
+      </c>
+      <c r="F45">
+        <v>741.559997558594</v>
+      </c>
+      <c r="G45">
+        <v>732.090026855469</v>
+      </c>
+      <c r="H45">
+        <v>741</v>
+      </c>
+      <c r="I45">
+        <v>746.138854980469</v>
+      </c>
+      <c r="J45">
+        <v>736.758056640625</v>
+      </c>
+      <c r="K45">
+        <v>58035200</v>
+      </c>
+      <c r="L45">
+        <v>-1.6276216506958</v>
+      </c>
+      <c r="M45">
+        <v>66.9716567993164</v>
+      </c>
+      <c r="N45">
+        <v>-9.74757289886475</v>
+      </c>
+      <c r="O45" t="s">
+        <v>1</v>
+      </c>
+      <c r="P45">
+        <v>62.1432952880859</v>
+      </c>
+      <c r="Q45">
+        <v>736.351501464844</v>
+      </c>
+      <c r="R45">
+        <v>737.890869140625</v>
+      </c>
+      <c r="S45">
+        <v>740.243469238281</v>
+      </c>
+      <c r="T45">
+        <v>4.578857421875</v>
+      </c>
+      <c r="U45">
+        <v>4.66802978515625</v>
+      </c>
+      <c r="V45">
+        <v>9.38079833984375</v>
       </c>
     </row>
   </sheetData>
